--- a/deliverables/plan/wbs.xlsx
+++ b/deliverables/plan/wbs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WBS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +447,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -457,7 +457,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1089,7 +1089,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">

--- a/deliverables/plan/wbs.xlsx
+++ b/deliverables/plan/wbs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WBS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +447,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -457,7 +457,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -534,16 +534,30 @@
           <t>[정책 학습]</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>32</v>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>0%</t>
@@ -554,7 +568,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>foothold-go2</t>
@@ -569,19 +587,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[평가 체계]</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>[작업] RoboGauge 공개 정책 4종: 우리 평가에 붙이기</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>32</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>0%</t>
@@ -592,10 +624,14 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
@@ -607,16 +643,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[작업] RoboGauge 공개 정책 4종: 우리 평가에 붙이기</t>
+          <t>[평가 체계]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,13 +661,13 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -646,12 +682,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
@@ -666,16 +702,30 @@
           <t>[작업] 에셋 팩 수령과 HDRI 렌더 테스트</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>0%</t>
@@ -686,7 +736,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -853,19 +907,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[작업] 도구 백과 — 우리가 쓰는 도구들을 그림과 함께</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>[승격 검토] inbox/meang/20260825-park-mentoring.md</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>18</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>0%</t>
@@ -876,7 +944,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -891,19 +963,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260825-park-mentoring.md</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>[작업] 도구 백과 — 우리가 쓰는 도구들을 그림과 함께</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>53</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>0%</t>
@@ -914,7 +1000,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -929,19 +1019,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[운영]</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>[인프라] Vaultwarden 개통 + NAS 폴더 구조</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>32</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>0%</t>
@@ -952,10 +1056,14 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
@@ -967,22 +1075,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[인프라] Vaultwarden 개통 + NAS 폴더 구조</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>[작업] 자동 분류 배선 시험 2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>18</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -990,7 +1116,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1005,42 +1135,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[작업] 자동 분류 배선 시험 2</t>
+          <t>[운영]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>FINAL · 최종발표</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18</v>
+        <v>122</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>vfxpedia</t>
@@ -1048,12 +1174,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/final/final-report.md</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1215,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1775,7 +1901,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">

--- a/deliverables/plan/wbs.xlsx
+++ b/deliverables/plan/wbs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WBS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -447,7 +447,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -457,7 +457,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -582,12 +582,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A3 평가</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[작업] RoboGauge 공개 정책 4종: 우리 평가에 붙이기</t>
+          <t>[작업] 실패 지형 5종 담당을 정한다</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -596,11 +596,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -608,15 +608,19 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -638,36 +642,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A3 평가</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[평가 체계]</t>
+          <t>[작업] 레일즈 MuJoCo 사전 측정과 Isaac 스윕 설계</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -677,68 +681,72 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A4 트윈·렌더</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[작업] 에셋 팩 수령과 HDRI 렌더 테스트</t>
+          <t>[작업] RunPod에서 Isaac 험지 지형 headless 생성·확인 환경 확보</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -750,27 +758,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B1 항법</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[작업] ROS 2 학습자료 01·ROS 2 개발환경 구축 정리</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+          <t>[작업] 험지 지형 종류 확장 및 난이도 파라미터화</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -778,7 +804,11 @@
           <t>less82</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -788,35 +818,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B1 항법</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[작업] ROS 2 학습자료 02·ROS 2 Python 프로그래밍 정리</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>[작업] 테스트</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>35</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -826,24 +878,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B1 항법</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[작업] ROS 2 학습자료 03·TF 좌표계와 RViz2 시각화 정리</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>[작업] 실패 지형 gap: 진단 -&gt; 레시피 (임석헌)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>34</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>0%</t>
@@ -851,10 +917,14 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>IQ152</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -864,24 +934,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B2 인지</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[작업] CV 담당 단계별 계획과 실행 환경 문서 제출</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>[작업] 실패 지형 rails: 진단 -&gt; 레시피 (맹라현)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>34</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>0%</t>
@@ -889,10 +973,14 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -902,36 +990,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260825-park-mentoring.md</t>
+          <t>[작업] 실패 지형 stepping_stones: 진단 -&gt; 레시피 (오현민)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -941,12 +1029,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -958,12 +1046,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[작업] 도구 백과 — 우리가 쓰는 도구들을 그림과 함께</t>
+          <t>[작업] 실패 지형 pit: 진단 -&gt; 레시피 (이민우)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -972,11 +1060,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -987,7 +1075,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -997,7 +1085,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>lmw0207</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1014,36 +1102,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[인프라] Vaultwarden 개통 + NAS 폴더 구조</t>
+          <t>[작업] 실패 지형 floating_ring: 진단 -&gt; 레시피 (오흥재)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1058,7 +1146,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1070,40 +1158,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>A2 지형·씬 제작</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[작업] 자동 분류 배선 시험 2</t>
+          <t>[작업] 파인튜닝 가능한 지형 조사</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1113,12 +1201,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1130,21 +1218,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[운영]</t>
+          <t>[작업] RoboGauge 공개 정책 4종: 우리 평가에 붙이기</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FINAL · 최종발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1153,13 +1241,13 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1169,29 +1257,29 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>vfxpedia,less82</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>deliverables/final/final-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[작업] 우분투 전환 후 DDP 재측정</t>
+          <t>[평가 체계]</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1215,7 +1303,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1235,42 +1323,60 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>A4 트윈·렌더</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[작업] 자동화 배선 테스트</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>[작업] 에셋 팩 수령과 HDRI 렌더 테스트</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>50</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1280,25 +1386,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[실험] 배선 테스트 - 담당자 자동 지정 확인</t>
+          <t>[작업] ROS 2 학습자료 01·ROS 2 개발환경 구축 정리</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1309,38 +1415,38 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[작업] 협업 규칙 문서 초안 작성</t>
+          <t>[작업] ROS 2 학습자료 02·ROS 2 Python 프로그래밍 정리</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1351,7 +1457,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1364,25 +1470,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[작업] 휘발 방지 — 결정 로그·검증 기록·재개 지점 문서화</t>
+          <t>[작업] ROS 2 학습자료 03·TF 좌표계와 RViz2 시각화 정리</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1393,7 +1499,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1406,39 +1512,53 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>B2 인지</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[작업] 협업 규칙 COLLAB.md 작성 + collab.html 게시</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t>[작업] CV 담당 단계별 계획과 실행 환경 문서 제출</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NAV · 실기 항법</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>74</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>deliverables/final/nav-report.md</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1448,36 +1568,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[막힘] 사이트 5개 페이지 다크모드 미지원</t>
+          <t>[작업] 노션 프로젝트 기획 정리</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>lmw0207</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1490,25 +1606,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[테스트] done date 자동 기입 검증</t>
+          <t>[작업] 저수준 이전·증류 잔재 정리 · 8/19 에 뺀 목표가 본문에 살아 있다</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1532,31 +1648,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[테스트] sub-issue 자동 연결 검증</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+          <t>[승격 검토] inbox/meang/20260825-park-mentoring.md</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>18</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1564,7 +1690,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1574,31 +1704,41 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[테스트] 루프 차단 후 sub-issue 재검증</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+          <t>[작업] 도구 백과 · 우리가 쓰는 도구들을 그림과 함께</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>53</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1606,7 +1746,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1616,31 +1760,41 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[실측] WS: DDP 판정 · 1,500 완주 · 평가 기준선 86.7% · 난이도 곡선</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t>[작업] 기술 레퍼런스 허브 신설 (허브 6번째)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>34</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1648,7 +1802,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1658,39 +1816,53 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[웹] 연구 페이지 시각화: 이미지 15장 · 영상 재생 · 썸네일 · NEW 배지 · em dash 관문</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+          <t>[작업] foothold-wiki 흡수 · 한 곳으로 모은다</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>34</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1700,31 +1872,41 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260814-pipeline-test.md</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+          <t>[작업] 허브 안 표현 재설계 · 위에서 아래로 흐르는 목록을 바꾼다</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>34</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1732,7 +1914,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1742,31 +1928,41 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/lim/20260822-베이스라인 모델의 간단한 미경험 험지 성능 측정.md</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+          <t>[작업] 사이트 온톨로지 정의 (무엇이 무엇의 상위인가)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>34</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1774,7 +1970,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1784,25 +1984,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260818-rough-terrain-rl-study.md</t>
+          <t>[작업] 조선대 저장소 이력 소실 · 실습 zip 4종을 잃었다</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -1826,31 +2026,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[작업] 자동 분류 배선 시험</t>
+          <t>[작업] 강의 저장소 감시가 알림만 한다. 미러까지 하게</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1868,58 +2064,1608 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>[작업] v2.0.0 적용 완료 점검 · 여덟 가지를 실측으로 확인한다</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>[작업] PRD-WEB 정렬 패스 · 기준 한 장대로 전 화면을 맞춘다</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>[작업] 표지를 타겟 기준으로 재구성 · 온톨로지의 마지막 축을 쓴다</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>[인프라] Vaultwarden 개통 + NAS 폴더 구조</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>32</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>[작업] 자동 분류 배선 시험 2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>18</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>[작업] RunPod 네트워크 볼륨 개설과 팀 폴더 구조 표준화</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>13</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>[운영]</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FINAL · 최종발표</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>122</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>deliverables/final/final-report.md</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>foothold-go2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>[작업] 우분투 전환 후 DDP 재측정</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>50</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>[작업] 일정 시스템 구현 (8/26 설계안이 통째로 증발했다)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>34</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>[작업] NEW 배지가 허브에서는 안 뜬다 (설계 재정비)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>34</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>[작업] 브랜드·테마 일관성: 전역바 로고가 정본이 아니다</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>34</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>[작업] WBS 자동 생성 결과가 웹에 도달하지 않는다</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>(미분류)</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>[작업] 자동화 배선 테스트</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>[실험] 배선 테스트 - 담당자 자동 지정 확인</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>foothold-go2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>[작업] 협업 규칙 문서 초안 작성</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>[작업] 휘발 방지 · 결정 로그·검증 기록·재개 지점 문서화</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>[작업] 협업 규칙 COLLAB.md 작성 + collab.html 게시</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>[막힘] 사이트 5개 페이지 다크모드 미지원</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>[테스트] done date 자동 기입 검증</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>[테스트] sub-issue 자동 연결 검증</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>[테스트] 루프 차단 후 sub-issue 재검증</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>[실측] WS: DDP 판정 · 1,500 완주 · 평가 기준선 86.7% · 난이도 곡선</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>[웹] 연구 페이지 시각화: 이미지 15장 · 영상 재생 · 썸네일 · NEW 배지 · em dash 관문</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/oh/20260814-pipeline-test.md</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/lim/20260822-베이스라인 모델의 간단한 미경험 험지 성능 측정.md</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/meang/20260818-rough-terrain-rl-study.md</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>[작업] 자동 분류 배선 시험</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/oh/20260826-ros2-01-개발환경구축.md</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>[주간] W35 팀 목표 (8/24~8/30)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>vfxpedia,less82,lmw0207,IQ152,maengu86</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>[주간] W36 오흥재 개인 목표</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>[주간] W36 맹라현 개인 목표</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>[주간] W36 오현민 개인 목표</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>[주간] W36 임석헌 개인 목표</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>IQ152</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>[주간] W36 이민우 개인 목표</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>lmw0207</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>[8/13] 조선대 방문: FIELD-CHECK 수행</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>A-정책</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D67" t="n">
         <v>32</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>48%</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>[주간] W36 팀 목표 (8/31~9/6) · 기획발표 주</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>vfxpedia,less82,lmw0207,IQ152,maengu86</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
         <is>
           <t>foothold-lab</t>
         </is>

--- a/deliverables/plan/wbs.xlsx
+++ b/deliverables/plan/wbs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WBS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -457,7 +457,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -531,36 +531,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[정책 학습]</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>32</v>
-      </c>
+          <t>[승격 검토] inbox/meang/20260818-rough-terrain-rl-study.md</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>61%</t>
-        </is>
-      </c>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -568,14 +558,10 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
@@ -587,7 +573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 5종 담당을 정한다</t>
+          <t>[정책 학습]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -596,11 +582,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -610,12 +596,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -635,7 +621,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
@@ -647,7 +633,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[작업] 레일즈 MuJoCo 사전 측정과 Isaac 스윕 설계</t>
+          <t>[작업] 실패 지형 5종 담당을 정한다</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -656,11 +642,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -668,20 +654,24 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -703,7 +693,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[작업] RunPod에서 Isaac 험지 지형 headless 생성·확인 환경 확보</t>
+          <t>[작업] 레일즈 MuJoCo 사전 측정과 Isaac 스윕 설계</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -712,11 +702,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -724,24 +714,20 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -763,7 +749,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[작업] 험지 지형 종류 확장 및 난이도 파라미터화</t>
+          <t>[작업] RunPod에서 Isaac 험지 지형 headless 생성·확인 환경 확보</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -791,7 +777,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -823,35 +809,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[작업] 테스트</t>
+          <t>[작업] 험지 지형 종류 확장 및 난이도 파라미터화</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -861,12 +847,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -883,31 +869,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 gap: 진단 -&gt; 레시피 (임석헌)</t>
+          <t>[작업] 평지 직진 기준선 수립 + 미경험 10종 동일 조건 재측정</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -917,12 +903,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>IQ152</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -939,7 +925,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 rails: 진단 -&gt; 레시피 (맹라현)</t>
+          <t>[작업] 테스트</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -948,11 +934,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -960,15 +946,19 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -995,7 +985,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 stepping_stones: 진단 -&gt; 레시피 (오현민)</t>
+          <t>[작업] 실패 지형 gap: 진단 -&gt; 레시피 (임석헌)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1019,7 +1009,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1029,7 +1019,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1051,7 +1041,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 pit: 진단 -&gt; 레시피 (이민우)</t>
+          <t>[작업] 실패 지형 rails: 진단 -&gt; 레시피 (맹라현)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1075,7 +1065,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1085,7 +1075,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>lmw0207</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1107,7 +1097,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 floating_ring: 진단 -&gt; 레시피 (오흥재)</t>
+          <t>[작업] 실패 지형 stepping_stones: 진단 -&gt; 레시피 (오현민)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1131,7 +1121,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1141,7 +1131,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1158,12 +1148,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A2 지형·씬 제작</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[작업] 파인튜닝 가능한 지형 조사</t>
+          <t>[작업] 실패 지형 pit: 진단 -&gt; 레시피 (이민우)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1172,11 +1162,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1184,11 +1174,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>12%</t>
@@ -1196,12 +1182,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>lmw0207</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1218,36 +1204,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A3 평가</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[작업] RoboGauge 공개 정책 4종: 우리 평가에 붙이기</t>
+          <t>[작업] 실패 지형 floating_ring: 진단 -&gt; 레시피 (오흥재)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1257,12 +1243,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>vfxpedia,less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1274,36 +1260,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A3 평가</t>
+          <t>A2 지형·씬 제작</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[평가 체계]</t>
+          <t>[작업] MuJoCo ↔ Isaac Sim 관측 차원 차이 조사: 결과를 어디까지 근거로 쓸 것인가</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1318,24 +1304,24 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A4 트윈·렌더</t>
+          <t>A2 지형·씬 제작</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[작업] 에셋 팩 수령과 HDRI 렌더 테스트</t>
+          <t>[작업] 파인튜닝 가능한 지형 조사</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1344,11 +1330,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1356,20 +1342,24 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1386,25 +1376,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B1 항법</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[작업] ROS 2 학습자료 01·ROS 2 개발환경 구축 정리</t>
+          <t>[실측] WS: DDP 판정 · 1,500 완주 · 평가 기준선 86.7% · 난이도 곡선</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1415,7 +1405,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1428,25 +1418,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B1 항법</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[작업] ROS 2 학습자료 02·ROS 2 Python 프로그래밍 정리</t>
+          <t>[승격 검토] inbox/lim/20260822-베이스라인 모델의 간단한 미경험 험지 성능 측정.md</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1457,7 +1447,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1470,39 +1460,53 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B1 항법</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[작업] ROS 2 학습자료 03·TF 좌표계와 RViz2 시각화 정리</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+          <t>[작업] RoboGauge 공개 정책 4종: 우리 평가에 붙이기</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>32</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>vfxpedia,less82</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1512,36 +1516,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B2 인지</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[작업] CV 담당 단계별 계획과 실행 환경 문서 제출</t>
+          <t>[작업] 제로베이스 보행 기준선: 직진 20 m 를 좌우 5 cm 안에서 걷는가</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NAV · 실기 항법</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1551,12 +1555,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>deliverables/final/nav-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1568,24 +1572,38 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[작업] 노션 프로젝트 기획 정리</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+          <t>[작업] 평가 지표 3종(평균 리턴 · 에피소드 길이 · 성공률) 적용과 판정 기준 문서화</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>0%</t>
@@ -1593,10 +1611,14 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>lmw0207</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1606,28 +1628,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[작업] 저수준 이전·증류 잔재 정리 · 8/19 에 뺀 목표가 본문에 살아 있다</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+          <t>[평가 체계]</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>50</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>100%</t>
@@ -1638,46 +1674,50 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>A4 트윈·렌더</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260825-park-mentoring.md</t>
+          <t>[작업] 에셋 팩 수령과 HDRI 렌더 테스트</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1692,7 +1732,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1704,53 +1744,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[작업] 도구 백과 · 우리가 쓰는 도구들을 그림과 함께</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>MVP · 중간발표</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>53</v>
-      </c>
+          <t>[작업] ROS 2 학습자료 01·ROS 2 개발환경 구축 정리</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/generalization-report.md</t>
-        </is>
-      </c>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1760,53 +1786,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[작업] 기술 레퍼런스 허브 신설 (허브 6번째)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>MVP · 중간발표</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>34</v>
-      </c>
+          <t>[작업] ROS 2 학습자료 02·ROS 2 Python 프로그래밍 정리</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/generalization-report.md</t>
-        </is>
-      </c>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1816,41 +1828,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[작업] foothold-wiki 흡수 · 한 곳으로 모은다</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>MVP · 중간발표</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>34</v>
-      </c>
+          <t>[작업] ROS 2 학습자료 03·TF 좌표계와 RViz2 시각화 정리</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1858,11 +1860,7 @@
           <t>less82</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/generalization-report.md</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1872,41 +1870,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[작업] 허브 안 표현 재설계 · 위에서 아래로 흐르는 목록을 바꾼다</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>MVP · 중간발표</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>34</v>
-      </c>
+          <t>[승격 검토] inbox/oh/20260826-ros2-01-개발환경구축.md</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1914,11 +1902,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/generalization-report.md</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1928,36 +1912,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>B2 인지</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[작업] 사이트 온톨로지 정의 (무엇이 무엇의 상위인가)</t>
+          <t>[작업] CV 담당 단계별 계획과 실행 환경 문서 제출</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>NAV · 실기 항법</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1967,12 +1951,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/final/nav-report.md</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -1984,25 +1968,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[작업] 조선대 저장소 이력 소실 · 실습 zip 4종을 잃었다</t>
+          <t>[작업] 협업 규칙 문서 초안 작성</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -2026,27 +2010,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[작업] 강의 저장소 감시가 알림만 한다. 미러까지 하게</t>
+          <t>[작업] 휘발 방지 · 결정 로그·검증 기록·재개 지점 문서화</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2064,27 +2052,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[작업] v2.0.0 적용 완료 점검 · 여덟 가지를 실측으로 확인한다</t>
+          <t>[작업] 협업 규칙 COLLAB.md 작성 + collab.html 게시</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2102,32 +2094,36 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[작업] PRD-WEB 정렬 패스 · 기준 한 장대로 전 화면을 맞춘다</t>
+          <t>[작업] 노션 프로젝트 기획 정리</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>lmw0207</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2140,27 +2136,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[작업] 표지를 타겟 기준으로 재구성 · 온톨로지의 마지막 축을 쓴다</t>
+          <t>[작업] 저수준 이전·증류 잔재 정리 · 8/19 에 뺀 목표가 본문에 살아 있다</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2178,12 +2178,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[인프라] Vaultwarden 개통 + NAS 폴더 구조</t>
+          <t>[8/13] 조선대 방문: FIELD-CHECK 수행</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2204,15 +2204,19 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2234,12 +2238,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[작업] 자동 분류 배선 시험 2</t>
+          <t>[승격 검토] inbox/meang/20260825-park-mentoring.md</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2262,12 +2266,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2294,12 +2298,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[작업] RunPod 네트워크 볼륨 개설과 팀 폴더 구조 표준화</t>
+          <t>[작업] 8/31 박철제 멘토링 음성 전사와 정리본</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2308,11 +2312,11 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2333,7 +2337,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2350,36 +2354,36 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[운영]</t>
+          <t>[작업] RunPod 영속 볼륨 경로 정정: 웹에 게시된 /workspace 안내 3곳을 /data 로</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FINAL · 최종발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>122</v>
+        <v>12</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2394,24 +2398,24 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>deliverables/final/final-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[작업] 우분투 전환 후 DDP 재측정</t>
+          <t>[작업] 도구 백과 · 우리가 쓰는 도구들을 그림과 함께</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2420,11 +2424,11 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2435,7 +2439,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2462,12 +2466,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[작업] 일정 시스템 구현 (8/26 설계안이 통째로 증발했다)</t>
+          <t>[작업] 기술 레퍼런스 허브 신설 (허브 6번째)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2488,15 +2492,19 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2518,12 +2526,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[작업] NEW 배지가 허브에서는 안 뜬다 (설계 재정비)</t>
+          <t>[작업] foothold-wiki 흡수 · 한 곳으로 모은다</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2547,7 +2555,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2557,7 +2565,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2574,12 +2582,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[작업] 브랜드·테마 일관성: 전역바 로고가 정본이 아니다</t>
+          <t>[작업] 허브 안 표현 재설계 · 위에서 아래로 흐르는 목록을 바꾼다</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2600,15 +2608,19 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2630,35 +2642,41 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[작업] WBS 자동 생성 결과가 웹에 도달하지 않는다</t>
+          <t>[작업] 사이트 온톨로지 정의 (무엇이 무엇의 상위인가)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>34</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2666,7 +2684,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2676,35 +2698,53 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[작업] 자동화 배선 테스트</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+          <t>[작업] 기술 허브 확장 3편 집필: Isaac Lab 실전 · MuJoCo · Omniverse</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>30</v>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2714,31 +2754,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[실험] 배선 테스트 - 담당자 자동 지정 확인</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+          <t>[작업] 일정 허브 대시보드화: 전체 일정 + 개인 일정 도식 · 프로젝트 보드 연동</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>30</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2746,41 +2796,55 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[작업] 협업 규칙 문서 초안 작성</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+          <t>[작업] WBS 웹 시각화: 98행 표를 «지금 어디까지 왔나»가 보이는 화면으로</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2788,7 +2852,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2798,25 +2866,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[작업] 휘발 방지 · 결정 로그·검증 기록·재개 지점 문서화</t>
+          <t>[작업] 자동화 배선 테스트</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2825,11 +2893,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
@@ -2840,25 +2904,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[작업] 협업 규칙 COLLAB.md 작성 + collab.html 게시</t>
+          <t>[실험] 배선 테스트 - 담당자 자동 지정 확인</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2875,14 +2939,14 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2924,7 +2988,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2966,7 +3030,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3008,7 +3072,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3050,12 +3114,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[실측] WS: DDP 판정 · 1,500 완주 · 평가 기준선 86.7% · 난이도 곡선</t>
+          <t>[웹] 연구 페이지 시각화: 이미지 15장 · 영상 재생 · 썸네일 · NEW 배지 · em dash 관문</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -3092,25 +3156,25 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[웹] 연구 페이지 시각화: 이미지 15장 · 영상 재생 · 썸네일 · NEW 배지 · em dash 관문</t>
+          <t>[승격 검토] inbox/oh/20260814-pipeline-test.md</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -3134,25 +3198,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260814-pipeline-test.md</t>
+          <t>[작업] 자동 분류 배선 시험</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -3176,25 +3240,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/lim/20260822-베이스라인 모델의 간단한 미경험 험지 성능 측정.md</t>
+          <t>[작업] 조선대 저장소 이력 소실 · 실습 zip 4종을 잃었다</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -3218,31 +3282,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260818-rough-terrain-rl-study.md</t>
+          <t>[작업] 강의 저장소 감시가 알림만 한다. 미러까지 하게</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3260,31 +3320,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[작업] 자동 분류 배선 시험</t>
+          <t>[작업] v2.0.0 적용 완료 점검 · 여덟 가지를 실측으로 확인한다</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3302,31 +3358,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260826-ros2-01-개발환경구축.md</t>
+          <t>[작업] PRD-WEB 정렬 패스 · 기준 한 장대로 전 화면을 맞춘다</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3344,19 +3396,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[주간] W35 팀 목표 (8/24~8/30)</t>
+          <t>[작업] 표지를 타겟 기준으로 재구성 · 온톨로지의 마지막 축을 쓴다</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -3369,7 +3421,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>vfxpedia,less82,lmw0207,IQ152,maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -3382,19 +3434,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[주간] W36 오흥재 개인 목표</t>
+          <t>[작업] 멘토링 질문 사전 취합 · 노션 설계안의 빠진 조각</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -3420,32 +3472,36 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[주간] W36 맹라현 개인 목표</t>
+          <t>[승격 검토] inbox/oh/20260831-runpod-환경구축.md</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -3458,24 +3514,38 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[주간] W36 오현민 개인 목표</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+          <t>[인프라] Vaultwarden 개통 + NAS 폴더 구조</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>32</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>0%</t>
@@ -3483,10 +3553,14 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3496,35 +3570,57 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[주간] W36 임석헌 개인 목표</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+          <t>[작업] 자동 분류 배선 시험 2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>18</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>IQ152</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3534,24 +3630,38 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[주간] W36 이민우 개인 목표</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+          <t>[작업] RunPod 네트워크 볼륨 개설과 팀 폴더 구조 표준화</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>13</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>0%</t>
@@ -3559,10 +3669,14 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>lmw0207</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3572,12 +3686,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[8/13] 조선대 방문: FIELD-CHECK 수행</t>
+          <t>[작업] 맹 개인 규정 v2.4: 작업 자리를 저장소 밖으로 옮긴다</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3586,11 +3700,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3600,12 +3714,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3615,7 +3729,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3632,40 +3746,966 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>(미분류)</t>
+          <t>C2 운영</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>[작업] 맹 개인 규정 v2.5: 이슈를 열면 바로 In Progress 로 잡는다</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>12</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>[운영]</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FINAL · 최종발표</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>122</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>deliverables/final/final-report.md</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>foothold-go2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>[작업] 우분투 전환 후 DDP 재측정</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>50</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>[작업] 일정 시스템 구현 (8/26 설계안이 통째로 증발했다)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>34</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>[작업] NEW 배지가 허브에서는 안 뜬다 (설계 재정비)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>34</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>[작업] 브랜드·테마 일관성: 전역바 로고가 정본이 아니다</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>34</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>웹 문서에 출처 이슈 표기</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>30</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>판 번호 자동 갱신</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>30</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>[작업] WBS 자동 생성 결과가 웹에 도달하지 않는다</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>8</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>[주간] W35 팀 목표 (8/24~8/30)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>8</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>vfxpedia,less82,lmw0207,IQ152,maengu86</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>[주간] W36 팀 목표 (8/31~9/6) · 기획발표 주</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>기획발표</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
+      <c r="D78" t="n">
+        <v>8</v>
+      </c>
+      <c r="E78" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
         <is>
           <t>vfxpedia,less82,lmw0207,IQ152,maengu86</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>[주간] W36 오흥재 개인 목표</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>8</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>[주간] W36 맹라현 개인 목표</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>8</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>[주간] W36 오현민 개인 목표</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>8</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>[주간] W36 임석헌 개인 목표</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>8</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>IQ152</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>[주간] W36 이민우 개인 목표</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>8</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>lmw0207</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>[작업] 오늘 하루 진행 관리: 이슈 상태를 In Progress 로 유지하며 작업</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t>foothold-lab</t>
         </is>

--- a/deliverables/plan/wbs.xlsx
+++ b/deliverables/plan/wbs.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1260,21 +1260,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A2 지형·씬 제작</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[작업] MuJoCo ↔ Isaac Sim 관측 차원 차이 조사: 결과를 어디까지 근거로 쓸 것인가</t>
+          <t>Go2 관절 각도 한계 기구학 계산 (5 cm 벽)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1321,50 +1321,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[작업] 파인튜닝 가능한 지형 조사</t>
+          <t>[작업] MuJoCo ↔ Isaac Sim 관측 차원 차이 조사: 결과를 어디까지 근거로 쓸 것인가</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1376,28 +1372,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A3 평가</t>
+          <t>A2 지형·씬 제작</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[실측] WS: DDP 판정 · 1,500 완주 · 평가 기준선 86.7% · 난이도 곡선</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>[작업] 파인튜닝 가능한 지형 조사</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>35</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>100%</t>
@@ -1405,10 +1415,14 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1423,20 +1437,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/lim/20260822-베이스라인 모델의 간단한 미경험 험지 성능 측정.md</t>
+          <t>[실측] WS: DDP 판정 · 1,500 완주 · 평가 기준선 86.7% · 난이도 곡선</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1465,48 +1479,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[작업] RoboGauge 공개 정책 4종: 우리 평가에 붙이기</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>32</v>
-      </c>
+          <t>[승격 검토] inbox/lim/20260822-베이스라인 모델의 간단한 미경험 험지 성능 측정.md</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>vfxpedia,less82</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[작업] 제로베이스 보행 기준선: 직진 20 m 를 좌우 5 cm 안에서 걷는가</t>
+          <t>[작업] RoboGauge 공개 정책 4종: 우리 평가에 붙이기</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1530,11 +1530,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1545,7 +1545,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia,less82</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[작업] 평가 지표 3종(평균 리턴 · 에피소드 길이 · 성공률) 적용과 판정 기준 문서화</t>
+          <t>[작업] 제로베이스 보행 기준선: 직진 20 m 를 좌우 5 cm 안에서 걷는가</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1633,40 +1633,36 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[평가 체계]</t>
+          <t>[작업] 평가 지표 3종(평균 리턴 · 에피소드 길이 · 성공률) 적용과 판정 기준 문서화</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1676,24 +1672,24 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A4 트윈·렌더</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[작업] 에셋 팩 수령과 HDRI 렌더 테스트</t>
+          <t>[평가 체계]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1714,7 +1710,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>41%</t>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1737,46 +1737,60 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B1 항법</t>
+          <t>A4 트윈·렌더</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[작업] ROS 2 학습자료 01·ROS 2 개발환경 구축 정리</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+          <t>[작업] 에셋 팩 수령과 HDRI 렌더 테스트</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>50</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1791,7 +1805,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[작업] ROS 2 학습자료 02·ROS 2 Python 프로그래밍 정리</t>
+          <t>[작업] ROS 2 학습자료 01·ROS 2 개발환경 구축 정리</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1833,7 +1847,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[작업] ROS 2 학습자료 03·TF 좌표계와 RViz2 시각화 정리</t>
+          <t>[작업] ROS 2 학습자료 02·ROS 2 Python 프로그래밍 정리</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1875,20 +1889,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260826-ros2-01-개발환경구축.md</t>
+          <t>[작업] ROS 2 학습자료 03·TF 좌표계와 RViz2 시각화 정리</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1899,7 +1913,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -1912,53 +1926,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B2 인지</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[작업] CV 담당 단계별 계획과 실행 환경 문서 제출</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>NAV · 실기 항법</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>74</v>
-      </c>
+          <t>[승격 검토] inbox/oh/20260826-ros2-01-개발환경구축.md</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-11-07</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>deliverables/final/nav-report.md</t>
-        </is>
-      </c>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1968,39 +1968,53 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>B2 인지</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[작업] 협업 규칙 문서 초안 작성</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+          <t>[작업] CV 담당 단계별 계획과 실행 환경 문서 제출</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NAV · 실기 항법</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>74</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>deliverables/final/nav-report.md</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2015,7 +2029,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[작업] 휘발 방지 · 결정 로그·검증 기록·재개 지점 문서화</t>
+          <t>[작업] 협업 규칙 문서 초안 작성</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -2057,7 +2071,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[작업] 협업 규칙 COLLAB.md 작성 + collab.html 게시</t>
+          <t>[작업] 휘발 방지 · 결정 로그·검증 기록·재개 지점 문서화</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -2070,7 +2084,7 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -2099,20 +2113,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[작업] 노션 프로젝트 기획 정리</t>
+          <t>[작업] 협업 규칙 COLLAB.md 작성 + collab.html 게시</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -2123,7 +2137,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>lmw0207</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2141,7 +2155,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[작업] 저수준 이전·증류 잔재 정리 · 8/19 에 뺀 목표가 본문에 살아 있다</t>
+          <t>[작업] 노션 프로젝트 기획 정리</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -2154,7 +2168,7 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2165,7 +2179,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>lmw0207</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2183,37 +2197,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[8/13] 조선대 방문: FIELD-CHECK 수행</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>32</v>
-      </c>
+          <t>[작업] 저수준 이전·증류 잔재 정리 · 8/19 에 뺀 목표가 본문에 살아 있다</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>100%</t>
@@ -2224,11 +2224,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2243,7 +2239,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260825-park-mentoring.md</t>
+          <t>[8/13] 조선대 방문: FIELD-CHECK 수행</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2252,26 +2248,26 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2303,7 +2299,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[작업] 8/31 박철제 멘토링 음성 전사와 정리본</t>
+          <t>[승격 검토] inbox/meang/20260825-park-mentoring.md</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2312,32 +2308,36 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[작업] RunPod 영속 볼륨 경로 정정: 웹에 게시된 /workspace 안내 3곳을 /data 로</t>
+          <t>[작업] 8/31 박철제 멘토링 음성 전사와 정리본</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2380,7 +2380,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>0%</t>
@@ -2388,12 +2392,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2415,31 +2419,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[작업] 도구 백과 · 우리가 쓰는 도구들을 그림과 함께</t>
+          <t>[작업] RunPod 영속 볼륨 경로 정정: 웹에 게시된 /workspace 안내 3곳을 /data 로</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2454,7 +2458,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2471,7 +2475,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[작업] 기술 레퍼런스 허브 신설 (허브 6번째)</t>
+          <t>[작업] 도구 백과 · 우리가 쓰는 도구들을 그림과 함께</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2480,11 +2484,11 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2492,19 +2496,15 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[작업] foothold-wiki 흡수 · 한 곳으로 모은다</t>
+          <t>[작업] 기술 레퍼런스 허브 신설 (허브 6번째)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2552,7 +2552,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>12%</t>
@@ -2560,12 +2564,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2587,7 +2591,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[작업] 허브 안 표현 재설계 · 위에서 아래로 흐르는 목록을 바꾼다</t>
+          <t>[작업] foothold-wiki 흡수 · 한 곳으로 모은다</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2608,11 +2612,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>12%</t>
@@ -2620,12 +2620,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[작업] 사이트 온톨로지 정의 (무엇이 무엇의 상위인가)</t>
+          <t>[작업] 허브 안 표현 재설계 · 위에서 아래로 흐르는 목록을 바꾼다</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2668,7 +2668,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>12%</t>
@@ -2676,7 +2680,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2703,7 +2707,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[작업] 기술 허브 확장 3편 집필: Isaac Lab 실전 · MuJoCo · Omniverse</t>
+          <t>[작업] 사이트 온톨로지 정의 (무엇이 무엇의 상위인가)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2712,11 +2716,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2727,7 +2731,7 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2759,7 +2763,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[작업] 일정 허브 대시보드화: 전체 일정 + 개인 일정 도식 · 프로젝트 보드 연동</t>
+          <t>[작업] 기술 허브 확장 3편 집필: Isaac Lab 실전 · MuJoCo · Omniverse</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2815,16 +2819,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[작업] WBS 웹 시각화: 98행 표를 «지금 어디까지 왔나»가 보이는 화면으로</t>
+          <t>[작업] 일정 허브 대시보드화: 전체 일정 + 개인 일정 도식 · 프로젝트 보드 연동</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>기획발표</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2833,7 +2837,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2854,7 +2858,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>deliverables/plan/wbs.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -2866,35 +2870,53 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[작업] 자동화 배선 테스트</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+          <t>[작업] WBS 웹 시각화: 98행 표를 «지금 어디까지 왔나»가 보이는 화면으로</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2904,28 +2926,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[실험] 배선 테스트 - 담당자 자동 지정 확인</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+          <t>[승격 검토] inbox/meang/20260901-park-mentoring.md</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>100%</t>
@@ -2936,49 +2972,67 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[막힘] 사이트 5개 페이지 다크모드 미지원</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+          <t>프로젝트 기획서 본문 작성 (9/4 제출)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>IQ152</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2993,20 +3047,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[테스트] done date 자동 기입 검증</t>
+          <t>[작업] 자동화 배선 테스트</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -3035,20 +3089,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>[테스트] sub-issue 자동 연결 검증</t>
+          <t>[실험] 배선 테스트 - 담당자 자동 지정 확인</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -3065,7 +3119,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
@@ -3077,14 +3131,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>[테스트] 루프 차단 후 sub-issue 재검증</t>
+          <t>[막힘] 사이트 5개 페이지 다크모드 미지원</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -3119,20 +3173,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[웹] 연구 페이지 시각화: 이미지 15장 · 영상 재생 · 썸네일 · NEW 배지 · em dash 관문</t>
+          <t>[테스트] done date 자동 기입 검증</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -3161,20 +3215,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260814-pipeline-test.md</t>
+          <t>[테스트] sub-issue 자동 연결 검증</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -3203,20 +3257,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[작업] 자동 분류 배선 시험</t>
+          <t>[테스트] 루프 차단 후 sub-issue 재검증</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -3245,20 +3299,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[작업] 조선대 저장소 이력 소실 · 실습 zip 4종을 잃었다</t>
+          <t>[웹] 연구 페이지 시각화: 이미지 15장 · 영상 재생 · 썸네일 · NEW 배지 · em dash 관문</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -3287,22 +3341,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[작업] 강의 저장소 감시가 알림만 한다. 미러까지 하게</t>
+          <t>[승격 검토] inbox/oh/20260814-pipeline-test.md</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3325,22 +3383,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[작업] v2.0.0 적용 완료 점검 · 여덟 가지를 실측으로 확인한다</t>
+          <t>[작업] 자동 분류 배선 시험</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3363,22 +3425,26 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[작업] PRD-WEB 정렬 패스 · 기준 한 장대로 전 화면을 맞춘다</t>
+          <t>[작업] 조선대 저장소 이력 소실 · 실습 zip 4종을 잃었다</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3401,14 +3467,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[작업] 표지를 타겟 기준으로 재구성 · 온톨로지의 마지막 축을 쓴다</t>
+          <t>[작업] 강의 저장소 감시가 알림만 한다. 미러까지 하게</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -3439,22 +3505,26 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[작업] 멘토링 질문 사전 취합 · 노션 설계안의 빠진 조각</t>
+          <t>[승격 검토] inbox/oh/20260831-runpod-환경구축.md</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3477,26 +3547,36 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260831-runpod-환경구축.md</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+          <t>[인프라] Vaultwarden 개통 + NAS 폴더 구조</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>32</v>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3504,7 +3584,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3519,7 +3603,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[인프라] Vaultwarden 개통 + NAS 폴더 구조</t>
+          <t>[작업] 자동 분류 배선 시험 2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3528,11 +3612,11 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3540,15 +3624,19 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3575,7 +3663,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[작업] 자동 분류 배선 시험 2</t>
+          <t>[작업] RunPod 네트워크 볼륨 개설과 팀 폴더 구조 표준화</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3584,11 +3672,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3596,24 +3684,20 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3635,7 +3719,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[작업] RunPod 네트워크 볼륨 개설과 팀 폴더 구조 표준화</t>
+          <t>[작업] 맹 개인 규정 v2.4: 작업 자리를 저장소 밖으로 옮긴다</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3644,11 +3728,11 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3656,20 +3740,24 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3691,7 +3779,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[작업] 맹 개인 규정 v2.4: 작업 자리를 저장소 밖으로 옮긴다</t>
+          <t>[작업] 맹 개인 규정 v2.5: 이슈를 열면 바로 In Progress 로 잡는다</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3751,35 +3839,35 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[작업] 맹 개인 규정 v2.5: 이슈를 열면 바로 In Progress 로 잡는다</t>
+          <t>[운영]</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>FINAL · 최종발표</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3789,17 +3877,17 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/final/final-report.md</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
@@ -3811,16 +3899,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[운영]</t>
+          <t>[작업] 우분투 전환 후 DDP 재측정</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FINAL · 최종발표</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3829,22 +3917,18 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3854,12 +3938,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>deliverables/final/final-report.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3955,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[작업] 우분투 전환 후 DDP 재측정</t>
+          <t>[작업] 일정 시스템 구현 (8/26 설계안이 통째로 증발했다)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3880,11 +3964,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3895,7 +3979,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3927,7 +4011,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[작업] 일정 시스템 구현 (8/26 설계안이 통째로 증발했다)</t>
+          <t>[작업] NEW 배지가 허브에서는 안 뜬다 (설계 재정비)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3983,7 +4067,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[작업] NEW 배지가 허브에서는 안 뜬다 (설계 재정비)</t>
+          <t>[작업] 브랜드·테마 일관성: 전역바 로고가 정본이 아니다</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4004,7 +4088,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>12%</t>
@@ -4012,7 +4100,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4039,7 +4127,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[작업] 브랜드·테마 일관성: 전역바 로고가 정본이 아니다</t>
+          <t>웹 문서에 출처 이슈 표기</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4048,11 +4136,11 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4060,19 +4148,15 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4099,7 +4183,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>웹 문서에 출처 이슈 표기</t>
+          <t>판 번호 자동 갱신</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4155,36 +4239,40 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>판 번호 자동 갱신</t>
+          <t>[작업] WBS 자동 생성 결과가 웹에 도달하지 않는다</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4194,7 +4282,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4211,7 +4299,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>[작업] WBS 자동 생성 결과가 웹에 도달하지 않는다</t>
+          <t>[주간] W35 팀 목표 (8/24~8/30)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4232,11 +4320,7 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>57%</t>
@@ -4244,12 +4328,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>vfxpedia,less82,lmw0207,IQ152,maengu86</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4271,7 +4355,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>[주간] W35 팀 목표 (8/24~8/30)</t>
+          <t>[주간] W36 팀 목표 (8/31~9/6) · 기획발표 주</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4327,7 +4411,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>[주간] W36 팀 목표 (8/31~9/6) · 기획발표 주</t>
+          <t>[주간] W36 오흥재 개인 목표</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4361,7 +4445,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>vfxpedia,less82,lmw0207,IQ152,maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4383,7 +4467,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>[주간] W36 오흥재 개인 목표</t>
+          <t>[주간] W36 맹라현 개인 목표</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4417,7 +4501,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4439,7 +4523,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>[주간] W36 맹라현 개인 목표</t>
+          <t>[주간] W36 오현민 개인 목표</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4473,7 +4557,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4495,7 +4579,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[주간] W36 오현민 개인 목표</t>
+          <t>[주간] W36 임석헌 개인 목표</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4529,7 +4613,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4551,7 +4635,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>[주간] W36 임석헌 개인 목표</t>
+          <t>[주간] W36 이민우 개인 목표</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4585,7 +4669,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>IQ152</t>
+          <t>lmw0207</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4607,7 +4691,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>[주간] W36 이민우 개인 목표</t>
+          <t>[작업] v2.0.0 적용 완료 점검 · 여덟 가지를 실측으로 확인한다</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4616,11 +4700,11 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4631,7 +4715,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4641,7 +4725,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>lmw0207</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -4663,7 +4747,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>[작업] 오늘 하루 진행 관리: 이슈 상태를 In Progress 로 유지하며 작업</t>
+          <t>[작업] PRD-WEB 정렬 패스 · 기준 한 장대로 전 화면을 맞춘다</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4672,11 +4756,11 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4687,7 +4771,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4706,6 +4790,174 @@
         </is>
       </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>[작업] 표지를 타겟 기준으로 재구성 · 온톨로지의 마지막 축을 쓴다</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>5</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>[작업] 멘토링 질문 사전 취합 · 노션 설계안의 빠진 조각</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>5</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>[작업] 오늘 하루 진행 관리: 이슈 상태를 In Progress 로 유지하며 작업</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t>foothold-lab</t>
         </is>

--- a/deliverables/plan/wbs.xlsx
+++ b/deliverables/plan/wbs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WBS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -447,7 +447,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -457,7 +457,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -714,15 +714,19 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -777,7 +781,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -837,7 +841,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -890,15 +894,19 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -925,50 +933,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[작업] 테스트</t>
+          <t>[작업] 기본 지형 6종에 대해서 정책 개선</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -985,36 +989,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 gap: 진단 -&gt; 레시피 (임석헌)</t>
+          <t>[작업] NVIDA checkpoint 기본 성능 분석 및 추가 학습 설계 분석</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1024,7 +1032,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1041,7 +1049,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 rails: 진단 -&gt; 레시피 (맹라현)</t>
+          <t>[작업] 테스트</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1050,11 +1058,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1062,15 +1070,19 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1097,7 +1109,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 stepping_stones: 진단 -&gt; 레시피 (오현민)</t>
+          <t>[작업] 실패 지형 gap: 진단 -&gt; 레시피 (임석헌)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1121,7 +1133,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1131,7 +1143,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1153,7 +1165,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 pit: 진단 -&gt; 레시피 (이민우)</t>
+          <t>[작업] 실패 지형 rails: 진단 -&gt; 레시피 (맹라현)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1177,7 +1189,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1187,7 +1199,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>lmw0207</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1209,7 +1221,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 floating_ring: 진단 -&gt; 레시피 (오흥재)</t>
+          <t>[작업] 실패 지형 stepping_stones: 진단 -&gt; 레시피 (오현민)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1233,7 +1245,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1243,7 +1255,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1265,7 +1277,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Go2 관절 각도 한계 기구학 계산 (5 cm 벽)</t>
+          <t>[작업] 실패 지형 pit: 진단 -&gt; 레시피 (이민우)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1274,11 +1286,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1289,17 +1301,17 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>lmw0207</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1316,43 +1328,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A2 지형·씬 제작</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[작업] MuJoCo ↔ Isaac Sim 관측 차원 차이 조사: 결과를 어디까지 근거로 쓸 것인가</t>
+          <t>[작업] 실패 지형 floating_ring: 진단 -&gt; 레시피 (오흥재)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>vfxpedia</t>
@@ -1360,7 +1372,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1372,12 +1384,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A2 지형·씬 제작</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[작업] 파인튜닝 가능한 지형 조사</t>
+          <t>Go2 관절 각도 한계 기구학 계산 (5 cm 벽)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1386,11 +1398,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1398,24 +1410,20 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1432,28 +1440,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A3 평가</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[실측] WS: DDP 판정 · 1,500 완주 · 평가 기준선 86.7% · 난이도 곡선</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>[리서치] 학습 보상에 발 높이 항이 없다는 확인</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>27</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>100%</t>
@@ -1461,10 +1483,14 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1474,39 +1500,53 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A3 평가</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/lim/20260822-베이스라인 모델의 간단한 미경험 험지 성능 측정.md</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+          <t>[리서치] 레일 통과와 보상 설계: 외부 문헌 여섯 편 대조</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>25</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1516,12 +1556,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A3 평가</t>
+          <t>A2 지형·씬 제작</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[작업] RoboGauge 공개 정책 4종: 우리 평가에 붙이기</t>
+          <t>[작업] MuJoCo ↔ Isaac Sim 관측 차원 차이 조사: 결과를 어디까지 근거로 쓸 것인가</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1530,11 +1570,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1545,7 +1585,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1555,7 +1595,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>vfxpedia,less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1572,41 +1612,45 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A3 평가</t>
+          <t>A2 지형·씬 제작</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[작업] 제로베이스 보행 기준선: 직진 20 m 를 좌우 5 cm 안에서 걷는가</t>
+          <t>[작업] 파인튜닝 가능한 지형 조사</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1616,7 +1660,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1633,36 +1677,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[작업] 평가 지표 3종(평균 리턴 · 에피소드 길이 · 성공률) 적용과 판정 기준 문서화</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>12</v>
-      </c>
+          <t>[실측] WS: DDP 판정 · 1,500 완주 · 평가 기준선 86.7% · 난이도 곡선</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1670,11 +1704,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1689,37 +1719,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[평가 체계]</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MVP · 중간발표</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>50</v>
-      </c>
+          <t>[승격 검토] inbox/lim/20260822-베이스라인 모델의 간단한 미경험 험지 성능 측정.md</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>41%</t>
-        </is>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>100%</t>
@@ -1730,35 +1746,31 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/generalization-report.md</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A4 트윈·렌더</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[작업] 에셋 팩 수령과 HDRI 렌더 테스트</t>
+          <t>[작업] RoboGauge 공개 정책 4종: 우리 평가에 붙이기</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1767,13 +1779,13 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1783,12 +1795,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>vfxpedia,less82</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1800,28 +1812,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B1 항법</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[작업] ROS 2 학습자료 01·ROS 2 개발환경 구축 정리</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t>[작업] 제로베이스 보행 기준선: 직진 20 m 를 좌우 5 cm 안에서 걷는가</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>100%</t>
@@ -1829,10 +1855,14 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1842,39 +1872,53 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B1 항법</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[작업] ROS 2 학습자료 02·ROS 2 Python 프로그래밍 정리</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+          <t>[작업] 평가 지표 3종(평균 리턴 · 에피소드 길이 · 성공률) 적용과 판정 기준 문서화</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1884,28 +1928,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B1 항법</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[작업] ROS 2 학습자료 03·TF 좌표계와 RViz2 시각화 정리</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+          <t>10 m 기준과 「멈춰서 한 발씩」 적용 범위 결정</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>100%</t>
@@ -1913,10 +1971,14 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1926,28 +1988,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B1 항법</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260826-ros2-01-개발환경구축.md</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+          <t>평가 하네스 확장 5건 · 새 기준으로 잴 수 있게 (A-정책 임계경로)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>100%</t>
@@ -1958,7 +2034,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -1968,36 +2048,36 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B2 인지</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[작업] CV 담당 단계별 계획과 실행 환경 문서 제출</t>
+          <t>험지 4종이 전역 np.random 을 써서 env 밖 굽기가 재현되지 않는다</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NAV · 실기 항법</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2007,12 +2087,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>deliverables/final/nav-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2024,39 +2104,53 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[작업] 협업 규칙 문서 초안 작성</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+          <t>[리서치] 레일즈 난이도 경계 탐색 · 여덟 칸 100판</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>9</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2066,28 +2160,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[작업] 휘발 방지 · 결정 로그·검증 기록·재개 지점 문서화</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+          <t>[평가 체계]</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>50</v>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>100%</t>
@@ -2098,38 +2206,56 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[작업] 협업 규칙 COLLAB.md 작성 + collab.html 게시</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+          <t>[리서치] 평지 직진 「10 m · 좌우 5 cm」에 견줄 외부 근거가 있나</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>28</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>100%</t>
@@ -2137,10 +2263,14 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2150,28 +2280,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[작업] 노션 프로젝트 기획 정리</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+          <t>[작업] 기획서 7-1 KPI 실측 근거 재작성 + 근거 없는 목표치 6건 정리</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>400%</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>100%</t>
@@ -2179,10 +2323,14 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>lmw0207</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2192,31 +2340,41 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[작업] 저수준 이전·증류 잔재 정리 · 8/19 에 뺀 목표가 본문에 살아 있다</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+          <t>[작업] 험지 원자료 CSV 열과 정본 요약의 최대 80 포인트 불일치 해소 · 판정 임계 표기</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>400%</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2224,7 +2382,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2234,21 +2396,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>A4 트윈·렌더</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[8/13] 조선대 방문: FIELD-CHECK 수행</t>
+          <t>[작업] 에셋 팩 수령과 HDRI 렌더 테스트</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2257,22 +2419,18 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2282,7 +2440,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2294,42 +2452,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260825-park-mentoring.md</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>18</v>
-      </c>
+          <t>[작업] ROS 2 학습자료 01·ROS 2 개발환경 구축 정리</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>100%</t>
@@ -2337,14 +2481,10 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2354,42 +2494,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[작업] 8/31 박철제 멘토링 음성 전사와 정리본</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>12</v>
-      </c>
+          <t>[작업] ROS 2 학습자료 02·ROS 2 Python 프로그래밍 정리</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>100%</t>
@@ -2397,14 +2523,10 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>maengu86</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2414,53 +2536,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[작업] RunPod 영속 볼륨 경로 정정: 웹에 게시된 /workspace 안내 3곳을 /data 로</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>12</v>
-      </c>
+          <t>[작업] ROS 2 학습자료 03·TF 좌표계와 RViz2 시각화 정리</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2470,41 +2578,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[작업] 도구 백과 · 우리가 쓰는 도구들을 그림과 함께</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>MVP · 중간발표</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>53</v>
-      </c>
+          <t>[승격 검토] inbox/oh/20260826-ros2-01-개발환경구축.md</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
-      </c>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2512,11 +2610,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/generalization-report.md</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2526,55 +2620,51 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>B2 인지</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[작업] 기술 레퍼런스 허브 신설 (허브 6번째)</t>
+          <t>[작업] CV 담당 단계별 계획과 실행 환경 문서 제출</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>NAV · 실기 항법</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/final/nav-report.md</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2591,48 +2681,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[작업] foothold-wiki 흡수 · 한 곳으로 모은다</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>MVP · 중간발표</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>34</v>
-      </c>
+          <t>[작업] 협업 규칙 문서 초안 작성</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/generalization-report.md</t>
-        </is>
-      </c>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2647,37 +2723,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[작업] 허브 안 표현 재설계 · 위에서 아래로 흐르는 목록을 바꾼다</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>MVP · 중간발표</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>34</v>
-      </c>
+          <t>[작업] 휘발 방지 · 결정 로그·검증 기록·재개 지점 문서화</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>100%</t>
@@ -2688,11 +2750,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/generalization-report.md</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2707,36 +2765,26 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[작업] 사이트 온톨로지 정의 (무엇이 무엇의 상위인가)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>MVP · 중간발표</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>34</v>
-      </c>
+          <t>[작업] 협업 규칙 COLLAB.md 작성 + collab.html 게시</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2744,11 +2792,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/generalization-report.md</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2763,48 +2807,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[작업] 기술 허브 확장 3편 집필: Isaac Lab 실전 · MuJoCo · Omniverse</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>MVP · 중간발표</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>30</v>
-      </c>
+          <t>[작업] 노션 프로젝트 기획 정리</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/generalization-report.md</t>
-        </is>
-      </c>
+          <t>lmw0207</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2819,36 +2849,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[작업] 일정 허브 대시보드화: 전체 일정 + 개인 일정 도식 · 프로젝트 보드 연동</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>MVP · 중간발표</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>30</v>
-      </c>
+          <t>[작업] 저수준 이전·증류 잔재 정리 · 8/19 에 뺀 목표가 본문에 살아 있다</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2856,11 +2876,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/generalization-report.md</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2875,36 +2891,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[작업] WBS 웹 시각화: 98행 표를 «지금 어디까지 왔나»가 보이는 화면으로</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>4</v>
-      </c>
+          <t>terrain-finetune-plan §4-2 번호 제목 부재로 절 참조 관문 [3.62] 실패</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2912,11 +2918,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2931,52 +2933,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260901-park-mentoring.md</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>4</v>
-      </c>
+          <t>발표 스토리라인 v1.0 검토 · Codex 수정 지시 (WBS 축 · fine-tuning 표현 · 신규 실측)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2991,48 +2971,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>프로젝트 기획서 본문 작성 (9/4 제출)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>4</v>
-      </c>
+          <t>[작업] 9/4 운영진 중간발표 심사 피드백 전사와 정리본</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>IQ152</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3042,28 +3008,42 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[작업] 자동화 배선 테스트</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+          <t>[8/13] 조선대 방문: FIELD-CHECK 수행</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>32</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>100%</t>
@@ -3074,7 +3054,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3084,28 +3068,42 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>[실험] 배선 테스트 - 담당자 자동 지정 확인</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+          <t>[승격 검토] inbox/meang/20260825-park-mentoring.md</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>18</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>100%</t>
@@ -3116,38 +3114,56 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>[막힘] 사이트 5개 페이지 다크모드 미지원</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+          <t>[작업] 8/31 박철제 멘토링 음성 전사와 정리본</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>100%</t>
@@ -3155,10 +3171,14 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3168,31 +3188,41 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[테스트] done date 자동 기입 검증</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+          <t>[작업] RunPod 영속 볼륨 경로 정정: 웹에 게시된 /workspace 안내 3곳을 /data 로</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>12</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3200,7 +3230,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3210,28 +3244,42 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[테스트] sub-issue 자동 연결 검증</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+          <t>[작업] 9/2 박철제 멘토링 음성 전사와 정리본</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>100%</t>
@@ -3239,10 +3287,14 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3252,28 +3304,42 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[테스트] 루프 차단 후 sub-issue 재검증</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+          <t>[작업] 조선대 협력 커리큘럼 요일 정정과 금요일 확정 결정 기록 신설</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>9</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>100%</t>
@@ -3284,7 +3350,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3294,31 +3364,41 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[웹] 연구 페이지 시각화: 이미지 15장 · 영상 재생 · 썸네일 · NEW 배지 · em dash 관문</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+          <t>[작업] 도구 백과 · 우리가 쓰는 도구들을 그림과 함께</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>53</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3326,7 +3406,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3336,28 +3420,42 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260814-pipeline-test.md</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+          <t>[작업] 기술 레퍼런스 허브 신설 (허브 6번째)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>34</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>100%</t>
@@ -3368,7 +3466,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3378,28 +3480,42 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[작업] 자동 분류 배선 시험</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+          <t>[작업] foothold-wiki 흡수 · 한 곳으로 모은다</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>34</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>100%</t>
@@ -3407,10 +3523,14 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3420,28 +3540,42 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[작업] 조선대 저장소 이력 소실 · 실습 zip 4종을 잃었다</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+          <t>[작업] 허브 안 표현 재설계 · 위에서 아래로 흐르는 목록을 바꾼다</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>34</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
           <t>100%</t>
@@ -3452,7 +3586,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3462,24 +3600,38 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[작업] 강의 저장소 감시가 알림만 한다. 미러까지 하게</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+          <t>[작업] 사이트 온톨로지 정의 (무엇이 무엇의 상위인가)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>34</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>0%</t>
@@ -3490,7 +3642,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3500,31 +3656,41 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260831-runpod-환경구축.md</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+          <t>[작업] 기술 허브 확장 3편 집필: Isaac Lab 실전 · MuJoCo · Omniverse</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>30</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3532,7 +3698,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -3542,36 +3712,36 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[인프라] Vaultwarden 개통 + NAS 폴더 구조</t>
+          <t>[작업] 일정 허브 대시보드화: 전체 일정 + 개인 일정 도식 · 프로젝트 보드 연동</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3586,7 +3756,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -3598,40 +3768,40 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[작업] 자동 분류 배선 시험 2</t>
+          <t>[작업] WBS 웹 시각화: 98행 표를 «지금 어디까지 왔나»가 보이는 화면으로</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>200%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3646,7 +3816,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -3658,51 +3828,55 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[작업] RunPod 네트워크 볼륨 개설과 팀 폴더 구조 표준화</t>
+          <t>[승격 검토] inbox/meang/20260901-park-mentoring.md</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>200%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -3714,21 +3888,21 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[작업] 맹 개인 규정 v2.4: 작업 자리를 저장소 밖으로 옮긴다</t>
+          <t>프로젝트 기획서 본문 작성 (9/4 제출)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3737,17 +3911,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>200%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3757,12 +3931,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -3774,21 +3948,21 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[작업] 맹 개인 규정 v2.5: 이슈를 열면 바로 In Progress 로 잡는다</t>
+          <t>9/4 기획발표 자료 제작</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3797,32 +3971,28 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
+          <t>200%</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -3834,45 +4004,41 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[운영]</t>
+          <t>팀원 포지션 키워드 신설과 대외 화면 반영</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FINAL · 최종발표</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>122</v>
+        <v>4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>200%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3882,53 +4048,57 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>deliverables/final/final-report.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[작업] 우분투 전환 후 DDP 재측정</t>
+          <t>[승격 검토] inbox/lim/20260901-프로젝트기획서-초안.hwp</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>200%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3938,7 +4108,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -3950,36 +4120,36 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[작업] 일정 시스템 구현 (8/26 설계안이 통째로 증발했다)</t>
+          <t>[작업] 9/4 제출용 WBS 공식 PDF 제작</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>400%</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3994,7 +4164,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4006,36 +4176,36 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[작업] NEW 배지가 허브에서는 안 뜬다 (설계 재정비)</t>
+          <t>[작업] 팀 역할·책임 정의서 공식 PDF 제작</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>400%</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4050,7 +4220,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4062,40 +4232,40 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[작업] 브랜드·테마 일관성: 전역바 로고가 정본이 아니다</t>
+          <t>[작업] 제출 문서 4종 문체·근거 정정과 무판표기 PDF 갱신</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>400%</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4110,7 +4280,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4122,43 +4292,43 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>웹 문서에 출처 이슈 표기</t>
+          <t>[작업] 정본 기획서 기반 한 장 요약본 + PDF 재작성</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
+          <t>400%</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="J73" t="inlineStr">
         <is>
           <t>vfxpedia</t>
@@ -4166,7 +4336,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4178,43 +4348,43 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>판 번호 자동 갱신</t>
+          <t>[작업] 9/4 기획 발표 벡터 도해 4종 제작</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
+          <t>400%</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>vfxpedia</t>
@@ -4222,7 +4392,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4239,37 +4409,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>[작업] WBS 자동 생성 결과가 웹에 도달하지 않는다</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>8</v>
-      </c>
+          <t>[작업] 자동화 배선 테스트</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>100%</t>
@@ -4280,11 +4436,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -4299,51 +4451,37 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>[주간] W35 팀 목표 (8/24~8/30)</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>8</v>
-      </c>
+          <t>[실험] 배선 테스트 - 담당자 자동 지정 확인</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>vfxpedia,less82,lmw0207,IQ152,maengu86</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
@@ -4355,48 +4493,34 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>[주간] W36 팀 목표 (8/31~9/6) · 기획발표 주</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>8</v>
-      </c>
+          <t>[막힘] 사이트 5개 페이지 다크모드 미지원</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>vfxpedia,less82,lmw0207,IQ152,maengu86</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -4411,36 +4535,26 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>[주간] W36 오흥재 개인 목표</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>8</v>
-      </c>
+          <t>[테스트] done date 자동 기입 검증</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4448,11 +4562,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -4467,48 +4577,34 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>[주간] W36 맹라현 개인 목표</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>8</v>
-      </c>
+          <t>[테스트] sub-issue 자동 연결 검증</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>maengu86</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -4523,48 +4619,34 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>[주간] W36 오현민 개인 목표</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>8</v>
-      </c>
+          <t>[테스트] 루프 차단 후 sub-issue 재검증</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -4579,48 +4661,34 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[주간] W36 임석헌 개인 목표</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>8</v>
-      </c>
+          <t>[웹] 연구 페이지 시각화: 이미지 15장 · 영상 재생 · 썸네일 · NEW 배지 · em dash 관문</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>IQ152</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -4635,48 +4703,34 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>[주간] W36 이민우 개인 목표</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>8</v>
-      </c>
+          <t>[승격 검토] inbox/oh/20260814-pipeline-test.md</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>lmw0207</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -4691,36 +4745,26 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>[작업] v2.0.0 적용 완료 점검 · 여덟 가지를 실측으로 확인한다</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>7</v>
-      </c>
+          <t>[작업] 자동 분류 배선 시험</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4728,11 +4772,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -4747,36 +4787,26 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>[작업] PRD-WEB 정렬 패스 · 기준 한 장대로 전 화면을 맞춘다</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>5</v>
-      </c>
+          <t>[작업] 조선대 저장소 이력 소실 · 실습 zip 4종을 잃었다</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4784,11 +4814,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -4803,33 +4829,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[작업] 표지를 타겟 기준으로 재구성 · 온톨로지의 마지막 축을 쓴다</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>5</v>
-      </c>
+          <t>[작업] 강의 저장소 감시가 알림만 한다. 미러까지 하게</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>0%</t>
@@ -4840,11 +4852,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -4859,36 +4867,26 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>[작업] 멘토링 질문 사전 취합 · 노션 설계안의 빠진 조각</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>5</v>
-      </c>
+          <t>[승격 검토] inbox/oh/20260831-runpod-환경구축.md</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4896,11 +4894,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -4915,49 +4909,3685 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>프로젝트 페이지 검색의 본문 색인 누락 (절 1500자 잘림)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>[인프라] Vaultwarden 개통 + NAS 폴더 구조</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>32</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>[작업] 자동 분류 배선 시험 2</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>18</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>[작업] RunPod 네트워크 볼륨 개설과 팀 폴더 구조 표준화</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>13</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>[작업] 맹 개인 규정 v2.4: 작업 자리를 저장소 밖으로 옮긴다</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>12</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>[작업] 맹 개인 규정 v2.5: 이슈를 열면 바로 In Progress 로 잡는다</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>12</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>저장소 역할 재정의를 운영 문서에 반영 (lab 개발 · go2 공개 승격)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>실험 템플릿 lab 이관과 「승격」 용어 분리 (저장소 재정의 여파)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>[작업] 연구 허브 Track A 실패 험지 5종 카드 절 신설</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>[작업] 연구 허브 험지 카드 후속 과제 중복 제거 · 5열 배치 · 칩 작성자 시각 표기 · 미분류 8건 분류</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>[운영]</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>FINAL · 최종발표</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>122</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>deliverables/final/final-report.md</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>foothold-go2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>[작업] 우분투 전환 후 DDP 재측정</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>50</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>[작업] 일정 시스템 구현 (8/26 설계안이 통째로 증발했다)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>34</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>[작업] NEW 배지가 허브에서는 안 뜬다 (설계 재정비)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>34</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>[작업] 브랜드·테마 일관성: 전역바 로고가 정본이 아니다</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>34</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>웹 문서에 출처 이슈 표기</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>30</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>판 번호 자동 갱신</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>30</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>공개 문서 금액 표기 정정과 redact 금액 탐지 개선</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>30</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>[작업] 빌드 실행 순서 결함 2건 수정과 생성물 커밋·정상 배포</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>28</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>[작업] LEDGER 열린 이슈 전수 자동 집계와 원장 반영</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>28</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>[작업] WBS 자동 생성 결과가 웹에 도달하지 않는다</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>8</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>143%</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>[주간] W35 팀 목표 (8/24~8/30)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>8</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>143%</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>vfxpedia,less82,lmw0207,IQ152,maengu86</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>[주간] W36 팀 목표 (8/31~9/6) · 기획발표 주</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>8</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>143%</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>vfxpedia,less82,lmw0207,IQ152,maengu86</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>[주간] W36 오흥재 개인 목표</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>8</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>143%</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>[주간] W36 맹라현 개인 목표</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>8</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>143%</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>[주간] W36 오현민 개인 목표</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>8</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>143%</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>[주간] W36 임석헌 개인 목표</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>8</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>143%</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>IQ152</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>[주간] W36 이민우 개인 목표</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>8</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>143%</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>lmw0207</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>[작업] v2.0.0 적용 완료 점검 · 여덟 가지를 실측으로 확인한다</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>7</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>150%</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>[작업] PRD-WEB 정렬 패스 · 기준 한 장대로 전 화면을 맞춘다</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>5</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>175%</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>[작업] 표지를 타겟 기준으로 재구성 · 온톨로지의 마지막 축을 쓴다</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>5</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>175%</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>[작업] 멘토링 질문 사전 취합 · 노션 설계안의 빠진 조각</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>5</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>175%</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
           <t>[작업] 오늘 하루 진행 관리: 이슈 상태를 In Progress 로 유지하며 작업</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>기획발표</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D119" t="n">
         <v>4</v>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr">
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>200%</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>웹 v2.0.0 확정과 공지</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>200%</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
         <is>
           <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>WBS 구현 단계 층 신설과 사람별 기여 축</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>200%</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>[작업] 표지 D-day 계산 결함 수정 · 경과 시간 기준을 KST 달력 날짜 차이로 교정</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>2</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>400%</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>[작업] 일정 허브 멘토링 D-day 주간 반복 반영 · 빌드 시점 고정값 제거</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>400%</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>C2 운영</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>[작업] 연구 허브 「후속 과제」 라벨 수와 칩 수 불일치 해소 · 상한 초과분 표기</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>400%</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/meang/20260903-rails-diagnosis.md</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/meang/20260903-rails-isaac-sweep-design.md</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/lim/20260903_기본값_1500iter_학습지형결과분석.md</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/meang/20260902-park-mentoring.md</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/lee/20260902-브레인스토밍-입력본.txt</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260903-report-v2-개정안.md</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260902-benchmark-setup-lim-지표표-정정안.md</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260903-ending-title/foothold-ending-title.html</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260904-roughcut/foothold-roughcut.mp4</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260904-roughcut/foothold-roughcut.mp4</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260904-roughcut/foothold-roughcut.mp4</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260904-roughcut/foothold-roughcut.mp4</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260904-roughcut/foothold-roughcut.mp4</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260904-launch/.gitignore</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260904-launch/.gitignore</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260904-launch/.gitignore</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260904-launch/.gitignore</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260904-launch/.gitignore</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260904-launch/SOUND-CRITERIA.md</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260904-launch/CONVERSION.md</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260904-launch/CONVERSION.md</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260904-launch/README-A.md</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>[작업] 웹에 남은 ASCII 도식 3블록의 SVG 전환</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>[작업] 원장 전수 절의 자동 동기화</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>[작업] 강화학습 멘토 첫 미팅 준비 (월 17:00)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/lim/20260904_NVIDIA공식체크포인트_속도단차교차평가분석.md</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/meang/20260902-flat-straight-baseline-10m.md</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/meang/20260903-직진성-외부표준.md</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/meang/20260904-발보상-시간아니고높이아님.md</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/meang/20260904-east-midterm-review.md</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>[승격 검토] inbox/jay/20260905-mentor-change.md</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>런칭 영상 재작업 · B 판 보정과 A 판 듄 2 재구성</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>9</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>런칭 영상 B 사운드 재교정과 A 키비주얼 여덟 장</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>9</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>A 후속 · 오프닝 · 엔딩 타이틀 재굽기 · 사운드 기준 기록</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>9</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>사운드 잰 자 정정(-ac 1)과 A 최종 조립 스크립트</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>9</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>foothold-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>-ac 1 다운믹스 설명에 출력 형식 조건을 넣는다</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>9</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
         <is>
           <t>foothold-lab</t>
         </is>

--- a/deliverables/plan/wbs.xlsx
+++ b/deliverables/plan/wbs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WBS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -5071,13 +5071,13 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -5573,13 +5573,13 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -5629,13 +5629,13 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -5745,13 +5745,13 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6582,7 +6582,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10042,7 +10042,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -10102,7 +10102,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="G176" t="inlineStr"/>
@@ -10158,7 +10158,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -10167,13 +10167,13 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11994,7 +11994,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -12003,13 +12003,13 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">

--- a/deliverables/plan/wbs.xlsx
+++ b/deliverables/plan/wbs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WBS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +447,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -457,7 +457,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -611,40 +611,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[정책 학습]</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>32</v>
-      </c>
+          <t>논문 구조 분석: mai-code 로 AME-2 · MARG · START 와 우리 1 단계 모듈 대조</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>197%</t>
-        </is>
-      </c>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -652,14 +634,10 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
@@ -671,40 +649,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 5종 담당을 정한다</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>18</v>
-      </c>
+          <t>2 단계 계획: AME-2 · START 논문 충실 구현과 Go2 학습 · 평가</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>276%</t>
-        </is>
-      </c>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -712,11 +672,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -731,52 +687,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[작업] 레일즈 MuJoCo 사전 측정과 Isaac 스윕 설계</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>14</v>
-      </c>
+          <t>최종 실험 흐름과 일정: NVIDIA · v2 · final (START → HiPAN) 비교 · 시연 · 디지털 트윈</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>331%</t>
-        </is>
-      </c>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>maengu86</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -791,7 +725,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[작업] RunPod에서 Isaac 험지 지형 headless 생성·확인 환경 확보</t>
+          <t>[정책 학습]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -800,11 +734,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -814,12 +748,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>350%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -829,7 +763,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -839,7 +773,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
@@ -851,7 +785,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[작업] 험지 지형 종류 확장 및 난이도 파라미터화</t>
+          <t>[작업] 실패 지형 5종 담당을 정한다</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -860,11 +794,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -874,12 +808,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>350%</t>
+          <t>318%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -889,7 +823,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -911,7 +845,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[작업] 평지 직진 기준선 수립 + 미경험 10종 동일 조건 재측정</t>
+          <t>[작업] 레일즈 MuJoCo 사전 측정과 Isaac 스윕 설계</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -920,11 +854,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -939,7 +873,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>373%</t>
+          <t>385%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -949,7 +883,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -971,7 +905,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[작업] 기본 지형 6종에 대해서 정책 개선</t>
+          <t>[작업] RunPod에서 Isaac 험지 지형 headless 생성·확인 환경 확보</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -980,11 +914,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -992,20 +926,24 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>433%</t>
+          <t>408%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>IQ152</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1027,7 +965,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[작업] NVIDA checkpoint 기본 성능 분석 및 추가 학습 설계 분석</t>
+          <t>[작업] 험지 지형 종류 확장 및 난이도 파라미터화</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1036,11 +974,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1050,12 +988,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>475%</t>
+          <t>408%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1065,7 +1003,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>IQ152</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1087,7 +1025,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[계획] 발 높이의 상수에서 명령으로의 전환 설계</t>
+          <t>[작업] 평지 직진 기준선 수립 + 미경험 10종 동일 조건 재측정</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1096,11 +1034,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1110,12 +1048,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>700%</t>
+          <t>436%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1147,7 +1085,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[작업] 레일즈 학습 레시피 한 장으로 모으기</t>
+          <t>[작업] 기본 지형 6종에 대해서 정책 개선</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1156,11 +1094,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1168,24 +1106,20 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1600%</t>
+          <t>511%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1207,7 +1141,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[계획] 실패 지형 공략 뼈대의 N차 누적 전환과 연구 보드 축 재구성</t>
+          <t>[작업] NVIDA checkpoint 기본 성능 분석 및 추가 학습 설계 분석</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1216,24 +1150,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>562%</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>100%</t>
@@ -1241,7 +1179,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1263,7 +1201,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[작업] E 정책 비교 영상 13종 촬영</t>
+          <t>[계획] 발 높이의 상수에서 명령으로의 전환 설계</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1272,11 +1210,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1289,7 +1227,11 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>840%</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>100%</t>
@@ -1319,35 +1261,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[작업] 테스트</t>
+          <t>[작업] 레일즈 학습 레시피 한 장으로 모으기</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>135%</t>
+          <t>1950%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1362,7 +1304,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1379,25 +1321,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 gap: 진단 -&gt; 레시피 (임석헌)</t>
+          <t>[계획] 실패 지형 공략 뼈대의 N차 누적 전환과 연구 보드 축 재구성</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1405,11 +1347,7 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>136%</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>100%</t>
@@ -1417,12 +1355,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>IQ152</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1439,25 +1377,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 rails: 진단 -&gt; 레시피 (맹라현)</t>
+          <t>[작업] E 정책 비교 영상 13종 촬영</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>34</v>
+        <v>-6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1465,11 +1403,7 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>136%</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>100%</t>
@@ -1477,12 +1411,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1499,7 +1433,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 stepping_stones: 진단 -&gt; 레시피 (오현민)</t>
+          <t>[작업] 테스트</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1508,11 +1442,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1522,12 +1456,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>136%</t>
+          <t>156%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1537,7 +1471,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1559,7 +1493,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 pit: 진단 -&gt; 레시피 (이민우)</t>
+          <t>[작업] 실패 지형 gap: 진단 -&gt; 레시피 (임석헌)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1587,7 +1521,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>136%</t>
+          <t>158%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1597,7 +1531,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>lmw0207</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1619,7 +1553,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 floating_ring: 진단 -&gt; 레시피 (오흥재)</t>
+          <t>[작업] 실패 지형 rails: 진단 -&gt; 레시피 (맹라현)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1647,7 +1581,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>136%</t>
+          <t>158%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1657,7 +1591,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1679,7 +1613,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Go2 관절 각도 한계 기구학 계산 (5 cm 벽)</t>
+          <t>[작업] 실패 지형 stepping_stones: 진단 -&gt; 레시피 (오현민)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1688,11 +1622,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1707,7 +1641,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>141%</t>
+          <t>158%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1717,7 +1651,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1739,7 +1673,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[리서치] 학습 보상에 발 높이 항이 없다는 확인</t>
+          <t>[작업] 실패 지형 pit: 진단 -&gt; 레시피 (이민우)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1748,11 +1682,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1762,12 +1696,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>146%</t>
+          <t>158%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1777,7 +1711,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>lmw0207</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1799,7 +1733,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[리서치] 레일 통과와 보상 설계: 외부 문헌 여섯 편 대조</t>
+          <t>[작업] 실패 지형 floating_ring: 진단 -&gt; 레시피 (오흥재)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1808,11 +1742,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1820,20 +1754,24 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>150%</t>
+          <t>158%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1855,7 +1793,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[작업] RL gap 30cm 범위까지 추가 학습 및 검증</t>
+          <t>Go2 관절 각도 한계 기구학 계산 (5 cm 벽)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1864,11 +1802,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1876,20 +1814,24 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>160%</t>
+          <t>166%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>IQ152</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1911,7 +1853,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[작업] foothold-v1.pt에서 rails 지형 추가 학습</t>
+          <t>[리서치] 학습 보상에 발 높이 항이 없다는 확인</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1920,11 +1862,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1934,12 +1876,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>173%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1949,7 +1891,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>IQ152</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1971,7 +1913,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[작업] 500 iter 실행 기록 복원 · 레시피 중간 단계</t>
+          <t>[리서치] 레일 통과와 보상 설계: 외부 문헌 여섯 편 대조</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1980,11 +1922,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1992,24 +1934,20 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>180%</t>
+          <t>179%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2031,7 +1969,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[작업] 레시피 계보 기록 · A·B 출발점과 설정 diff</t>
+          <t>[작업] RL gap 30cm 범위까지 추가 학습 및 검증</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2040,11 +1978,11 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2052,24 +1990,20 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>180%</t>
+          <t>195%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2091,7 +2025,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[작업] 명령 능력 복원 D 학습 · 정지·저속·회전 프로브 신설과 기준선 측정</t>
+          <t>[작업] foothold-v1.pt에서 rails 지형 추가 학습</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2100,11 +2034,11 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2114,12 +2048,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>200%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2129,7 +2063,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2151,7 +2085,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[작업] E 환경 설정과 Isaac Lab 등록</t>
+          <t>[작업] 500 iter 실행 기록 복원 · 레시피 중간 단계</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2160,11 +2094,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2179,7 +2113,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>209%</t>
+          <t>227%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2211,7 +2145,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[조사] 지각 논문 MARG · HiPAN · AME-2 정밀 검토</t>
+          <t>[작업] 레시피 계보 기록 · A·B 출발점과 설정 diff</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2220,11 +2154,11 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2239,7 +2173,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>233%</t>
+          <t>227%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2271,7 +2205,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[계획] 험지 통과와 기본 명령을 함께 학습하는 연구 방향 정리</t>
+          <t>[작업] 명령 능력 복원 D 학습 · 정지·저속·회전 프로브 신설과 기준선 측정</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2280,11 +2214,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2294,12 +2228,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1300%</t>
+          <t>258%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2326,17 +2260,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A2 지형·씬 제작</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[작업] MuJoCo ↔ Isaac Sim 관측 차원 차이 조사: 결과를 어디까지 근거로 쓸 것인가</t>
+          <t>[작업] E 환경 설정과 Isaac Lab 등록</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2344,12 +2278,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2359,7 +2293,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>373%</t>
+          <t>273%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2374,7 +2308,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2386,12 +2320,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A2 지형·씬 제작</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[작업] 파인튜닝 가능한 지형 조사</t>
+          <t>[조사] 지각 논문 MARG · HiPAN · AME-2 정밀 검토</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2400,11 +2334,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2414,12 +2348,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>135%</t>
+          <t>311%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2429,7 +2363,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2446,28 +2380,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A3 평가</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[실측] WS: DDP 판정 · 1,500 완주 · 평가 기준선 86.7% · 난이도 곡선</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+          <t>[계획] 험지 통과와 기본 명령을 함께 학습하는 연구 방향 정리</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2000%</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>100%</t>
@@ -2478,7 +2426,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2488,28 +2440,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A3 평가</t>
+          <t>A2 지형·씬 제작</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/lim/20260822-베이스라인 모델의 간단한 미경험 험지 성능 측정.md</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+          <t>[작업] MuJoCo ↔ Isaac Sim 관측 차원 차이 조사: 결과를 어디까지 근거로 쓸 것인가</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>436%</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>100%</t>
@@ -2520,7 +2486,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2530,40 +2500,40 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A3 평가</t>
+          <t>A2 지형·씬 제작</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[작업] RoboGauge 공개 정책 4종: 우리 평가에 붙이기</t>
+          <t>[작업] 파인튜닝 가능한 지형 조사</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>197%</t>
+          <t>156%</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2573,12 +2543,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>vfxpedia,less82</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2595,37 +2565,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[작업] 제로베이스 보행 기준선: 직진 20 m 를 좌우 5 cm 안에서 걷는가</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>12</v>
-      </c>
+          <t>[실측] WS: DDP 판정 · 1,500 완주 · 평가 기준선 86.7% · 난이도 곡선</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>373%</t>
-        </is>
-      </c>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>100%</t>
@@ -2633,14 +2589,10 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>maengu86</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2655,37 +2607,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[작업] 평가 지표 3종(평균 리턴 · 에피소드 길이 · 성공률) 적용과 판정 기준 문서화</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>12</v>
-      </c>
+          <t>[승격 검토] inbox/lim/20260822-베이스라인 모델의 간단한 미경험 험지 성능 측정.md</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>373%</t>
-        </is>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>100%</t>
@@ -2696,11 +2634,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2715,7 +2649,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10 m 기준과 「멈춰서 한 발씩」 적용 범위 결정</t>
+          <t>[작업] RoboGauge 공개 정책 4종: 우리 평가에 붙이기</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2724,11 +2658,11 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2738,12 +2672,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>373%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2753,7 +2687,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>vfxpedia,less82</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2775,7 +2709,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>평가 하네스 확장 5건 · 새 기준으로 잴 수 있게 (A-정책 임계경로)</t>
+          <t>[작업] 제로베이스 보행 기준선: 직진 20 m 를 좌우 5 cm 안에서 걷는가</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2784,11 +2718,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2798,12 +2732,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>400%</t>
+          <t>436%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2813,7 +2747,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2835,7 +2769,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>험지 4종이 전역 np.random 을 써서 env 밖 굽기가 재현되지 않는다</t>
+          <t>[작업] 평가 지표 3종(평균 리턴 · 에피소드 길이 · 성공률) 적용과 판정 기준 문서화</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2844,11 +2778,11 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2863,7 +2797,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>433%</t>
+          <t>436%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2895,7 +2829,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[리서치] 레일즈 난이도 경계 탐색 · 여덟 칸 100 에피소드</t>
+          <t>10 m 기준과 「멈춰서 한 발씩」 적용 범위 결정</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2904,11 +2838,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2918,12 +2852,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>475%</t>
+          <t>436%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2933,7 +2867,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2955,7 +2889,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[작업] 지형 혼합 학습 5개 arm 동일 평가지형 비교 (stepping 41 + rough 회귀 16)</t>
+          <t>평가 하네스 확장 5건 · 새 기준으로 잴 수 있게 (A-정책 임계경로)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2964,11 +2898,11 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2978,12 +2912,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>850%</t>
+          <t>470%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2993,7 +2927,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3015,7 +2949,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[작업] 평가 코드 조용한 오작동 3건 기록과 재발 방지 절차</t>
+          <t>험지 4종이 전역 np.random 을 써서 env 밖 굽기가 재현되지 않는다</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3024,11 +2958,11 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3036,20 +2970,24 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>850%</t>
+          <t>511%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3071,7 +3009,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[작업] 험지 집계에서 평지 지형의 분리</t>
+          <t>[리서치] 레일즈 난이도 경계 탐색 · 여덟 칸 100 에피소드</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3080,11 +3018,11 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3094,12 +3032,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>850%</t>
+          <t>562%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3109,7 +3047,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3131,7 +3069,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[작업] 지형 검사 관문이 검사 실패를 못 막는다 · 러너 종료 코드 계약 복구</t>
+          <t>[작업] 지형 혼합 학습 5개 arm 동일 평가지형 비교 (stepping 41 + rough 회귀 16)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3152,15 +3090,19 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>850%</t>
+          <t>1025%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3187,7 +3129,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[작업] 부동소수점 절단으로 지형 치수가 조용히 틀어진다 · round 스냅 적용</t>
+          <t>[작업] 평가 코드 조용한 오작동 3건 기록과 재발 방지 절차</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3211,7 +3153,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>850%</t>
+          <t>1025%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3243,7 +3185,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[작업] 지형 검사기 신뢰성 2건 · horizontal_scale 미전파와 생성기 함수 하드코딩</t>
+          <t>[작업] 험지 집계에서 평지 지형의 분리</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3264,20 +3206,24 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>850%</t>
+          <t>1025%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3299,7 +3245,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>[작업] play_eval.py 스윕 지형 선택 스위치 신설 (--terrain_cfg)</t>
+          <t>[작업] 지형 검사 관문이 검사 실패를 못 막는다 · 러너 종료 코드 계약 복구</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3323,7 +3269,7 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>850%</t>
+          <t>1025%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3355,7 +3301,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>[결정] 방향 판정 기준이 코드·정본CSV·원장에서 서로 다른 문제</t>
+          <t>[작업] 부동소수점 절단으로 지형 치수가 조용히 틀어진다 · round 스냅 적용</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3376,24 +3322,20 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>850%</t>
+          <t>1025%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3415,7 +3357,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[실험] 징검다리 메시 해상도별 발 접촉 물리 검증</t>
+          <t>[작업] 지형 검사기 신뢰성 2건 · horizontal_scale 미전파와 생성기 함수 하드코딩</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3436,19 +3378,15 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>850%</t>
+          <t>1025%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3475,7 +3413,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[리서치] 리셋을 쓰는 평가에서 같은 명령줄로 다시 돌리면 «관절까지» 같은 판이 나오나</t>
+          <t>[작업] play_eval.py 스윕 지형 선택 스위치 신설 (--terrain_cfg)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3484,11 +3422,11 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3496,24 +3434,20 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1100%</t>
+          <t>1025%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3535,7 +3469,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[작업] 평가 하네스가 죽어도 종료코드 0 을 내는 문제</t>
+          <t>[결정] 방향 판정 기준이 코드·정본CSV·원장에서 서로 다른 문제</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3544,11 +3478,11 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3556,15 +3490,19 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1100%</t>
+          <t>1025%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3591,7 +3529,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[작업] 평가 프로토콜 정본 1장 작성 · 난이도 주축과 고정값 확정</t>
+          <t>[실험] 징검다리 메시 해상도별 발 접촉 물리 검증</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3600,11 +3538,11 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3614,12 +3552,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1100%</t>
+          <t>1025%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3629,7 +3567,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3651,7 +3589,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[작업] 벤치마크 관문의 성공 조건과 종료코드 계약 문서화</t>
+          <t>[리서치] 리셋을 쓰는 평가에서 같은 명령줄로 다시 돌리면 «관절까지» 같은 판이 나오나</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3674,12 +3612,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1100%</t>
+          <t>1333%</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3689,7 +3627,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3711,40 +3649,36 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[평가 체계]</t>
+          <t>[작업] 평가 하네스가 죽어도 종료코드 0 을 내는 문제</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>124%</t>
+          <t>1333%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3754,12 +3688,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
@@ -3771,35 +3705,35 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[리서치] 평지 직진 「10 m · 좌우 5 cm」에 견줄 외부 근거가 있나</t>
+          <t>[작업] 평가 프로토콜 정본 1장 작성 · 난이도 주축과 고정값 확정</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>144%</t>
+          <t>1333%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3809,12 +3743,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3831,35 +3765,35 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[작업] 명령속도 5단 보폭 실측 · 유도값 39 cm 대체</t>
+          <t>[작업] 벤치마크 관문의 성공 조건과 종료코드 계약 문서화</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>155%</t>
+          <t>1333%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3869,12 +3803,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3891,7 +3825,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[작업] 미세 틈 일반화 평가 · horizontal_scale 0.025 구간 해상도와 브리지 대조군</t>
+          <t>[평가 체계]</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3900,11 +3834,11 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3914,12 +3848,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>155%</t>
+          <t>139%</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3929,7 +3863,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3939,7 +3873,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3885,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[작업] RoboGauge 점수표 기여 철회의 문서 반영 · 한 문서 안 두 판 정리</t>
+          <t>[리서치] 평지 직진 「10 m · 좌우 5 cm」에 견줄 외부 근거가 있나</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3960,11 +3894,11 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3972,20 +3906,24 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>157%</t>
+          <t>170%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4007,7 +3945,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[작업] 갤러리 컷 포스터 이미지 생성과 목록 지연 로딩</t>
+          <t>[작업] 명령속도 5단 보폭 실측 · 유도값 39 cm 대체</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4016,11 +3954,11 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4030,12 +3968,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>163%</t>
+          <t>186%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4045,7 +3983,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4067,7 +4005,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[작업] 대조컷 선택 정책의 코드화와 색인 기록</t>
+          <t>[작업] 미세 틈 일반화 평가 · horizontal_scale 0.025 구간 해상도와 브리지 대조군</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4076,11 +4014,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4090,12 +4028,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>163%</t>
+          <t>186%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4105,7 +4043,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4127,7 +4065,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[작업] 지형 집합과 모델별 학습 노출의 분리</t>
+          <t>[작업] RoboGauge 점수표 기여 철회의 문서 반영 · 한 문서 안 두 판 정리</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4136,11 +4074,11 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4148,19 +4086,15 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>163%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4187,7 +4121,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[작업] 갤러리 컷의 안정 식별자와 재촬영 이력 기록</t>
+          <t>[작업] 갤러리 컷 포스터 이미지 생성과 목록 지연 로딩</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4215,7 +4149,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>163%</t>
+          <t>200%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4247,7 +4181,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[작업] gap 참여도 표시 정정 · 0.03 % 표본 숫자가 100 % 표본과 같아 보이는 문제</t>
+          <t>[작업] 대조컷 선택 정책의 코드화와 색인 기록</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4256,11 +4190,11 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4275,7 +4209,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>186%</t>
+          <t>200%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4307,7 +4241,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[작업] 학습 명령 범위와 평가 범위 대조 관문 · 범위 밖 평가점 부재 시 배포 차단</t>
+          <t>[작업] 지형 집합과 모델별 학습 노출의 분리</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4316,11 +4250,11 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4328,7 +4262,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>200%</t>
@@ -4336,7 +4274,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4363,7 +4301,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[작업] 정책 계보·판정 기준 2차 독립 감사</t>
+          <t>[작업] 갤러리 컷의 안정 식별자와 재촬영 이력 기록</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4372,11 +4310,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4391,7 +4329,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>271%</t>
+          <t>200%</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4423,7 +4361,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[작업] 판정 코드에 CRITERIA v1.3 반영 · 제외 규칙 철회와 요약 병합 신원 검사</t>
+          <t>[작업] gap 참여도 표시 정정 · 0.03 % 표본 숫자가 100 % 표본과 같아 보이는 문제</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4432,11 +4370,11 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4444,15 +4382,19 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>271%</t>
+          <t>236%</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4479,7 +4421,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[작업] 학습 device 교란과 재현성 6차 독립 감사</t>
+          <t>[작업] 학습 명령 범위와 평가 범위 대조 관문 · 범위 밖 평가점 부재 시 배포 차단</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4488,11 +4430,11 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4500,19 +4442,15 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>300%</t>
+          <t>258%</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4539,7 +4477,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[판정] 후보 1 · v2b-r iter2500 · 축 2 첫 9/9 (확정 후보 아님)</t>
+          <t>[작업] 정책 계보·판정 기준 2차 독립 감사</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4548,11 +4486,11 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4567,7 +4505,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>300%</t>
+          <t>371%</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4599,7 +4537,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>[작업] 학습량·발 보상·신경망 실험 우선순위 감사</t>
+          <t>[작업] 판정 코드에 CRITERIA v1.3 반영 · 제외 규칙 철회와 요약 병합 신원 검사</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4608,11 +4546,11 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4620,19 +4558,15 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>300%</t>
+          <t>371%</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4659,7 +4593,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>[검증] 처음부터 학습 전환의 계보·통계·실험 조건 감사</t>
+          <t>[작업] 학습 device 교란과 재현성 6차 독립 감사</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4668,11 +4602,11 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4687,7 +4621,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>500%</t>
+          <t>417%</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4719,7 +4653,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>[실험] 처음부터 학습 전환 · fs1·fs2 와 장치 교차 짝</t>
+          <t>[판정] 후보 1 · v2b-r iter2500 · 축 2 첫 9/9 (확정 후보 아님)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4728,11 +4662,11 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4747,7 +4681,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>500%</t>
+          <t>417%</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4779,7 +4713,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>[평가] 축 2 문턱이 잡음보다 좁다 · n=64 에서 fell_ratio 0.10 판정 재설계</t>
+          <t>[작업] 학습량·발 보상·신경망 실험 우선순위 감사</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4788,11 +4722,11 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4800,15 +4734,19 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>500%</t>
+          <t>417%</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4835,7 +4773,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>[검증] v2 MVP 후보 원자료 재계산과 발표 주장 감사</t>
+          <t>[검증] 처음부터 학습 전환의 계보·통계·실험 조건 감사</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4844,11 +4782,11 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4858,12 +4796,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>700%</t>
+          <t>733%</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4895,35 +4833,35 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>[작업] 기획서 7-1 KPI 실측 근거 재작성 + 근거 없는 목표치 6건 정리</t>
+          <t>[실험] 처음부터 학습 전환 · fs1·fs2 와 장치 교차 짝</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>기획발표</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>3900%</t>
+          <t>733%</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4938,7 +4876,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>deliverables/plan/wbs.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -4955,40 +4893,36 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>[작업] 험지 원자료 CSV 열과 정본 요약의 최대 80 포인트 불일치 해소 · 판정 임계 표기</t>
+          <t>[평가] 축 2 문턱이 잡음보다 좁다 · n=64 에서 fell_ratio 0.10 판정 재설계</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>기획발표</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>3900%</t>
+          <t>733%</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4998,7 +4932,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>deliverables/plan/wbs.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5010,27 +4944,45 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A4 트윈·렌더</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[이후 과제] 디지털 트윈 방법의 실제 적용 (ASTRA-MVP 와)</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
+          <t>[검증] v2 MVP 후보 원자료 재계산과 발표 주장 감사</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>3</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1050%</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5038,7 +4990,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -5048,41 +5004,45 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A4 트윈·렌더</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>[작업] 맹라현 Vercel 배포 화면 분석 · PR #543 수정본 기준</t>
+          <t>[작업] 기획서 7-1 KPI 실측 근거 재작성 + 근거 없는 목표치 6건 정리</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FINAL · 최종발표</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>4600%</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5092,7 +5052,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>deliverables/final/final-report.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5104,30 +5064,30 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A4 트윈·렌더</t>
+          <t>A3 평가</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>[작업] 에셋 팩 수령과 HDRI 렌더 테스트</t>
+          <t>[작업] 험지 원자료 CSV 열과 정본 요약의 최대 80 포인트 불일치 해소 · 판정 임계 표기</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5137,7 +5097,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>124%</t>
+          <t>4600%</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5152,7 +5112,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5169,40 +5129,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>[작업] 3DGS 지형 PoC · 스마트폰 영상 지면 메시화와 Isaac Sim Go2 보행 검증</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>MVP · 중간발표</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>15</v>
-      </c>
+          <t>[이후 과제] 디지털 트윈 방법의 실제 적용 (ASTRA-MVP 와)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>186%</t>
-        </is>
-      </c>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5210,11 +5152,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/generalization-report.md</t>
-        </is>
-      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -5229,37 +5167,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[작업] 트윈 렌더 마스터 14컷 전멸 · CUDA_VISIBLE_DEVICES 로 인한 RTX 렌더러 GPU 스킵과 프레임 수 미검증</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>MVP · 중간발표</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>15</v>
-      </c>
+          <t>[작업] GIST 3DGS 결과 NAS 보존 사전 동의 요청</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>186%</t>
-        </is>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>100%</t>
@@ -5270,11 +5194,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/generalization-report.md</t>
-        </is>
-      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -5289,50 +5209,46 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>[작업] 3DGS 실공간 복원 파이프라인 실측 + COLMAP·GLOMAP 비교 + 촬영 지침 수립</t>
+          <t>[작업] 맹라현 Vercel 배포 화면 분석 · PR #543 수정본 기준</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>FINAL · 최종발표</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>186%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/final/final-report.md</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5344,28 +5260,42 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B1 항법</t>
+          <t>A4 트윈·렌더</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>[작업] ROS 2 학습자료 01·ROS 2 개발환경 구축 정리</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
+          <t>[작업] 에셋 팩 수령과 HDRI 렌더 테스트</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>50</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>139%</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>100%</t>
@@ -5373,10 +5303,14 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -5386,28 +5320,42 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B1 항법</t>
+          <t>A4 트윈·렌더</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>[작업] ROS 2 학습자료 02·ROS 2 Python 프로그래밍 정리</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
+          <t>[작업] 3DGS 지형 PoC · 스마트폰 영상 지면 메시화와 Isaac Sim Go2 보행 검증</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>15</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>236%</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>100%</t>
@@ -5415,10 +5363,14 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -5428,28 +5380,42 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B1 항법</t>
+          <t>A4 트윈·렌더</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>[작업] ROS 2 학습자료 03·TF 좌표계와 RViz2 시각화 정리</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
+          <t>[작업] 트윈 렌더 마스터 14컷 전멸 · CUDA_VISIBLE_DEVICES 로 인한 RTX 렌더러 GPU 스킵과 프레임 수 미검증</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>15</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>236%</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>100%</t>
@@ -5457,10 +5423,14 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -5470,28 +5440,42 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B1 항법</t>
+          <t>A4 트윈·렌더</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260826-ros2-01-개발환경구축.md</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
+          <t>[작업] 3DGS 실공간 복원 파이프라인 실측 + COLMAP·GLOMAP 비교 + 촬영 지침 수립</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>15</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>236%</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>100%</t>
@@ -5499,10 +5483,14 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -5517,27 +5505,31 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>[이후 과제] 앱 + 전체 시스템 아키텍처: ROS2 - SLAM - Nav2 - 경로 탐색 · 미션 앱(로봇↔사용자) · 빠른 판단 하이브리드 (ASTRA-MVP 와)</t>
+          <t>[작업] ROS 2 학습자료 01·ROS 2 개발환경 구축 정리</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5555,36 +5547,26 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[작업] 시뮬 자체 planner 기반 목표 명령 속도 1.0 m/s 실측 (평지 직진·회전·정지 -&gt; 제동 거리 -&gt; 장애물·gap·rail)</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>NAV · 실기 항법</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>76</v>
-      </c>
+          <t>[작업] ROS 2 학습자료 02·ROS 2 Python 프로그래밍 정리</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5592,11 +5574,7 @@
           <t>less82</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>deliverables/final/nav-report.md</t>
-        </is>
-      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -5611,36 +5589,26 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[작업] 빈 평지 ㄱ자 센서 Nav 기본 검증 · 기존 정책 명령 1.0 m/s · LiDAR 점유지도 자체 planner</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>NAV · 실기 항법</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>76</v>
-      </c>
+          <t>[작업] ROS 2 학습자료 03·TF 좌표계와 RViz2 시각화 정리</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5648,11 +5616,7 @@
           <t>less82</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>deliverables/final/nav-report.md</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -5662,42 +5626,28 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B2 인지</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>[작업] CV 담당 단계별 계획과 실행 환경 문서 제출</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>NAV · 실기 항법</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>97</v>
-      </c>
+          <t>[승격 검토] inbox/oh/20260826-ros2-01-개발환경구축.md</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>49%</t>
-        </is>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>100%</t>
@@ -5705,14 +5655,10 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>deliverables/final/nav-report.md</t>
-        </is>
-      </c>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -5722,38 +5668,24 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B2 인지</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>[작업] CV 사람 검출 모델 재선정 오프라인 비교 (fasterrcnn_resnet50_fpn_v2 기준, 저장 영상 동일 입력)</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>NAV · 실기 항법</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>76</v>
-      </c>
+          <t>[이후 과제] 앱 + 전체 시스템 아키텍처: ROS2 - SLAM - Nav2 - 경로 탐색 · 미션 앱(로봇↔사용자) · 빠른 판단 하이브리드 (ASTRA-MVP 와)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>0%</t>
@@ -5761,14 +5693,10 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>less82</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>deliverables/final/nav-report.md</t>
-        </is>
-      </c>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -5778,39 +5706,53 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>[작업] 협업 규칙 COLLAB.md 작성 + collab.html 게시</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
+          <t>[작업] 시뮬 자체 planner 기반 목표 명령 속도 1.0 m/s 실측 (평지 직진·회전·정지 -&gt; 제동 거리 -&gt; 장애물·gap·rail)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>NAV · 실기 항법</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>76</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>deliverables/final/nav-report.md</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -5820,39 +5762,53 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>B1 항법</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>[작업] 노션 프로젝트 기획 정리</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
+          <t>[작업] 빈 평지 ㄱ자 센서 Nav 기본 검증 · 기존 정책 명령 1.0 m/s · LiDAR 점유지도 자체 planner</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>NAV · 실기 항법</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>76</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>lmw0207</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>deliverables/final/nav-report.md</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -5862,28 +5818,42 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>B2 인지</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>[작업] 저수준 이전·증류 잔재 정리 · 8/19 에 뺀 목표가 본문에 살아 있다</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
+          <t>[작업] CV 담당 단계별 계획과 실행 환경 문서 제출</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>NAV · 실기 항법</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>97</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>100%</t>
@@ -5891,10 +5861,14 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>deliverables/final/nav-report.md</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -5904,39 +5878,53 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>C1 기록</t>
+          <t>B2 인지</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>terrain-finetune-plan §4-2 번호 제목 부재로 절 참조 관문 [3.62] 실패</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
+          <t>[작업] CV 사람 검출 모델 재선정 오프라인 비교 (fasterrcnn_resnet50_fpn_v2 기준, 저장 영상 동일 입력)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>NAV · 실기 항법</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>76</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
+          <t>less82</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>deliverables/final/nav-report.md</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -5951,20 +5939,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>발표 스토리라인 v1.0 검토 · Codex 수정 지시 (WBS 축 · fine-tuning 표현 · 신규 실측)</t>
+          <t>[작업] 노션 프로젝트 기획 정리</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -5975,7 +5963,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>lmw0207</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -5993,20 +5981,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260903-report-v2-개정안.md</t>
+          <t>[작업] 저수준 이전·증류 잔재 정리 · 8/19 에 뺀 목표가 본문에 살아 있다</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -6035,20 +6023,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>[작업] 9/4 운영진 중간발표 심사 피드백 전사와 정리본</t>
+          <t>terrain-finetune-plan §4-2 번호 제목 부재로 절 참조 관문 [3.62] 실패</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -6059,7 +6047,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6077,22 +6065,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>[덱 보강] 왜 필요한가 · 명확한 사용자 · 비즈니스 연결 · 서비스 앱 (MVP 피드백 · ASTRA-MVP 와)</t>
+          <t>발표 스토리라인 v1.0 검토 · Codex 수정 지시 (WBS 축 · fine-tuning 표현 · 신규 실측)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6115,22 +6107,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>[요청] 10/7 팀원 진행 상황 보고 · 무엇을 · 기술적으로 어떻게 · 어디까지</t>
+          <t>[승격 검토] inbox/jay/20260903-report-v2-개정안.md</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6153,37 +6149,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>[8/13] 조선대 방문: FIELD-CHECK 수행</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>32</v>
-      </c>
+          <t>[작업] 9/4 운영진 중간발표 심사 피드백 전사와 정리본</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>197%</t>
-        </is>
-      </c>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>100%</t>
@@ -6191,14 +6173,10 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -6213,40 +6191,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260825-park-mentoring.md</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>18</v>
-      </c>
+          <t>[덱 보강] 왜 필요한가 · 명확한 사용자 · 비즈니스 연결 · 서비스 앱 (MVP 피드백 · ASTRA-MVP 와)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>276%</t>
-        </is>
-      </c>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6254,11 +6214,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -6273,52 +6229,30 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>[작업] 8/31 박철제 멘토링 음성 전사와 정리본</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>12</v>
-      </c>
+          <t>[요청] 10/7 팀원 진행 상황 보고 · 무엇을 · 기술적으로 어떻게 · 어디까지</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>373%</t>
-        </is>
-      </c>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>maengu86</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -6333,7 +6267,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[작업] RunPod 영속 볼륨 경로 정정: 웹에 게시된 /workspace 안내 3곳을 /data 로</t>
+          <t>[8/13] 조선대 방문: FIELD-CHECK 수행</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6342,11 +6276,11 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6356,12 +6290,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>373%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6393,7 +6327,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>[작업] 9/2 박철제 멘토링 음성 전사와 정리본</t>
+          <t>[승격 검토] inbox/meang/20260825-park-mentoring.md</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6402,11 +6336,11 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6416,12 +6350,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>433%</t>
+          <t>318%</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6431,7 +6365,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6453,7 +6387,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[작업] 조선대 협력 커리큘럼 요일 정정과 금요일 확정 결정 기록 신설</t>
+          <t>[작업] 8/31 박철제 멘토링 음성 전사와 정리본</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6462,11 +6396,11 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6476,12 +6410,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>475%</t>
+          <t>436%</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6491,7 +6425,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6513,7 +6447,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>[작업] 용어 범위 · KPI 고정 시점 · PRD 근거 정정 셋의 결정 로그 반영</t>
+          <t>[작업] RunPod 영속 볼륨 경로 정정: 웹에 게시된 /workspace 안내 3곳을 /data 로</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6522,11 +6456,11 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6541,7 +6475,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1100%</t>
+          <t>436%</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6573,35 +6507,35 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>[작업] 서비스 방향·차별점·근거 재검토 결과 정리 및 제출</t>
+          <t>[작업] 9/2 박철제 멘토링 음성 전사와 정리본</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FINAL · 최종발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>511%</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6616,7 +6550,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>deliverables/final/final-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -6633,35 +6567,35 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>[작업] 도구 백과 · 우리가 쓰는 도구들을 그림과 함께</t>
+          <t>[작업] 조선대 협력 커리큘럼 요일 정정과 금요일 확정 결정 기록 신설</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>123%</t>
+          <t>562%</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6676,7 +6610,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -6693,35 +6627,35 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[작업] 기술 레퍼런스 허브 신설 (허브 6번째)</t>
+          <t>[작업] 용어 범위 · KPI 고정 시점 · PRD 근거 정정 셋의 결정 로그 반영</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>136%</t>
+          <t>1333%</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6736,7 +6670,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6753,35 +6687,35 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[작업] foothold-wiki 흡수 · 한 곳으로 모은다</t>
+          <t>[작업] 서비스 방향·차별점·근거 재검토 결과 정리 및 제출</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>FINAL · 최종발표</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>136%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6791,12 +6725,12 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/final/final-report.md</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -6813,7 +6747,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[작업] 허브 안 표현 재설계 · 위에서 아래로 흐르는 목록을 바꾼다</t>
+          <t>[작업] 기술 레퍼런스 허브 신설 (허브 6번째)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6841,7 +6775,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>136%</t>
+          <t>158%</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6873,7 +6807,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[작업] 사이트 온톨로지 정의 (무엇이 무엇의 상위인가)</t>
+          <t>[작업] foothold-wiki 흡수 · 한 곳으로 모은다</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6896,12 +6830,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>136%</t>
+          <t>158%</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -6911,7 +6845,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -6933,7 +6867,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>[작업] 기술 허브 확장 3편 집필: Isaac Lab 실전 · MuJoCo · Omniverse</t>
+          <t>[작업] 허브 안 표현 재설계 · 위에서 아래로 흐르는 목록을 바꾼다</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6942,26 +6876,26 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>141%</t>
+          <t>158%</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6993,7 +6927,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>[작업] 일정 허브 대시보드화: 전체 일정 + 개인 일정 도식 · 프로젝트 보드 연동</t>
+          <t>[작업] 사이트 온톨로지 정의 (무엇이 무엇의 상위인가)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7002,11 +6936,11 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7021,7 +6955,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>141%</t>
+          <t>158%</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7053,7 +6987,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>[작업] 발표 서사 정본과 계획 WBS 세로축의 결정 로그 반영</t>
+          <t>[작업] 기술 허브 확장 3편 집필: Isaac Lab 실전 · MuJoCo · Omniverse</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7062,11 +6996,11 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7081,7 +7015,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>157%</t>
+          <t>166%</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7113,7 +7047,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>[작업] 종합보고서 본문의 「판」 38곳을 「에피소드」로 · 관문 패턴 동기화</t>
+          <t>[작업] 일정 허브 대시보드화: 전체 일정 + 개인 일정 도식 · 프로젝트 보드 연동</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7122,11 +7056,11 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7136,12 +7070,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>166%</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7173,7 +7107,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>[작업] 문서 22개에 남은 「판」 290곳의 「에피소드」 치환과 관문</t>
+          <t>[작업] 발표 서사 정본과 계획 WBS 세로축의 결정 로그 반영</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7182,11 +7116,11 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7196,12 +7130,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7233,7 +7167,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>[작업] 평가 정본의 도식 중복 5개와 캡션 번호 소실</t>
+          <t>[작업] 종합보고서 본문의 「판」 38곳을 「에피소드」로 · 관문 패턴 동기화</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7261,7 +7195,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7293,7 +7227,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>[작업] 도해 21장의 viewBox 여백 불균일과 글자 겹침 1곳</t>
+          <t>[작업] 문서 22개에 남은 「판」 290곳의 「에피소드」 치환과 관문</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7321,7 +7255,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7353,7 +7287,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>[작업] Go2 도해에 로봇이 안 그려짐 · img 로 불린 SVG 의 바깥 자원</t>
+          <t>[작업] 평가 정본의 도식 중복 5개와 캡션 번호 소실</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7381,7 +7315,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7413,7 +7347,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>[작업] 종합보고서와 평가 정본의 역할 분리 · 첫머리를 핵심 발견으로</t>
+          <t>[작업] 도해 21장의 viewBox 여백 불균일과 글자 겹침 1곳</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7436,12 +7370,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7473,7 +7407,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>[작업] 「판」 잔여 74곳 정리와 예외 규칙 확정</t>
+          <t>[작업] Go2 도해에 로봇이 안 그려짐 · img 로 불린 SVG 의 바깥 자원</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7496,12 +7430,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7533,7 +7467,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>[계획] 팔레트 밖 색을 쓰는 도해 5장의 다크 처리 결정</t>
+          <t>[작업] 종합보고서와 평가 정본의 역할 분리 · 첫머리를 핵심 발견으로</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7556,12 +7490,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7593,7 +7527,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>[작업] 40일 넘게 안 고친 「지금을 말하는 문서」 3장 갱신</t>
+          <t>[작업] 「판」 잔여 74곳 정리와 예외 규칙 확정</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7602,11 +7536,11 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7621,7 +7555,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>180%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7653,7 +7587,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>[문서] FOOTHOLD MVP 종합보고서 HTML·PDF 제출본</t>
+          <t>[계획] 팔레트 밖 색을 쓰는 도해 5장의 다크 처리 결정</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7662,11 +7596,11 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7676,12 +7610,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>1300%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7713,7 +7647,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>[작업] MVP 대체 산출물 안내 PDF 4종</t>
+          <t>[작업] 40일 넘게 안 고친 「지금을 말하는 문서」 3장 갱신</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7722,11 +7656,11 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -7736,12 +7670,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>1300%</t>
+          <t>227%</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7773,7 +7707,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[작업] MVP 발표 서사·목차 설계와 합의사항 기록</t>
+          <t>[문서] FOOTHOLD MVP 종합보고서 HTML·PDF 제출본</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7796,12 +7730,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>1300%</t>
+          <t>2000%</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7833,7 +7767,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>[조사] GitHub Star 저장소 용도와 발표 시각화 후보 정리</t>
+          <t>[작업] MVP 대체 산출물 안내 PDF 4종</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7856,12 +7790,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>1300%</t>
+          <t>2000%</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7893,7 +7827,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>[후속] 브랜드 영상 기존 자산 인계와 제작 재개</t>
+          <t>[작업] MVP 발표 서사·목차 설계와 합의사항 기록</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7902,23 +7836,31 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2000%</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7945,35 +7887,35 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>[작업] 10/1 멘토링 회의록 정리·제출</t>
+          <t>[조사] GitHub Star 저장소 용도와 발표 시각화 후보 정리</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>NAV · 실기 항법</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>2000%</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7983,12 +7925,12 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>deliverables/final/nav-report.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8005,40 +7947,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>[작업] WBS 웹 시각화: 98행 표를 «지금 어디까지 왔나»가 보이는 화면으로</t>
+          <t>[후속] 브랜드 영상 기존 자산 인계와 제작 재개</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>기획발표</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>1367%</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8048,7 +7982,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>deliverables/plan/wbs.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8065,35 +7999,35 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260901-park-mentoring.md</t>
+          <t>[작업] 10/1 멘토링 회의록 정리·제출</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>기획발표</t>
+          <t>NAV · 실기 항법</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>1367%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8103,12 +8037,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>deliverables/plan/wbs.md</t>
+          <t>deliverables/final/nav-report.md</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8125,7 +8059,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>프로젝트 기획서 본문 작성 (9/4 제출)</t>
+          <t>[작업] WBS 웹 시각화: 98행 표를 «지금 어디까지 왔나»가 보이는 화면으로</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8148,12 +8082,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>1367%</t>
+          <t>1600%</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8163,7 +8097,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>IQ152</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8185,7 +8119,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>9/4 기획발표 자료 제작</t>
+          <t>[승격 검토] inbox/meang/20260901-park-mentoring.md</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8208,12 +8142,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>1367%</t>
+          <t>1600%</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8245,7 +8179,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>팀원 포지션 키워드 신설과 대외 화면 반영</t>
+          <t>프로젝트 기획서 본문 작성 (9/4 제출)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8268,12 +8202,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>1367%</t>
+          <t>1600%</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8283,7 +8217,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8305,7 +8239,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/lim/20260901-프로젝트기획서-초안.hwp</t>
+          <t>9/4 기획발표 자료 제작</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8328,12 +8262,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>1367%</t>
+          <t>1600%</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8365,7 +8299,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>[작업] 9/4 제출용 WBS 공식 PDF 제작</t>
+          <t>팀원 포지션 키워드 신설과 대외 화면 반영</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8374,11 +8308,11 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -8388,12 +8322,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>3900%</t>
+          <t>1600%</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8425,7 +8359,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>[작업] 팀 역할·책임 정의서 공식 PDF 제작</t>
+          <t>[승격 검토] inbox/lim/20260901-프로젝트기획서-초안.hwp</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8434,11 +8368,11 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8448,12 +8382,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>3900%</t>
+          <t>1600%</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8485,7 +8419,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[작업] 제출 문서 4종 문체·근거 정정과 무판표기 PDF 갱신</t>
+          <t>[작업] 9/4 제출용 WBS 공식 PDF 제작</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8508,12 +8442,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>3900%</t>
+          <t>4600%</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8545,7 +8479,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[작업] 정본 기획서 기반 한 장 요약본 + PDF 재작성</t>
+          <t>[작업] 팀 역할·책임 정의서 공식 PDF 제작</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8568,12 +8502,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>3900%</t>
+          <t>4600%</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8605,7 +8539,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>[작업] 9/4 기획 발표 벡터 도해 4종 제작</t>
+          <t>[작업] 제출 문서 4종 문체·근거 정정과 무판표기 PDF 갱신</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8628,12 +8562,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>3900%</t>
+          <t>4600%</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8660,28 +8594,42 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[실험] 배선 테스트 - 담당자 자동 지정 확인</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
+          <t>[작업] 정본 기획서 기반 한 장 요약본 + PDF 재작성</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>2</v>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr"/>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>4600%</t>
+        </is>
+      </c>
       <c r="I147" t="inlineStr">
         <is>
           <t>100%</t>
@@ -8692,38 +8640,56 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>C1 기록</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>[막힘] 사이트 5개 페이지 다크모드 미지원</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
+          <t>[작업] 9/4 기획 발표 벡터 도해 4종 제작</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>기획발표</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>2</v>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>4600%</t>
+        </is>
+      </c>
       <c r="I148" t="inlineStr">
         <is>
           <t>100%</t>
@@ -8734,7 +8700,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>deliverables/plan/wbs.md</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -8749,20 +8719,20 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>[테스트] done date 자동 기입 검증</t>
+          <t>[실험] 배선 테스트 - 담당자 자동 지정 확인</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
@@ -8779,7 +8749,7 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8761,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>[테스트] sub-issue 자동 연결 검증</t>
+          <t>[테스트] 루프 차단 후 sub-issue 재검증</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -8833,20 +8803,20 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>[테스트] 루프 차단 후 sub-issue 재검증</t>
+          <t>[웹] 연구 페이지 시각화: 이미지 15장 · 영상 재생 · 썸네일 · NEW 배지 · em dash 관문</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -8875,20 +8845,20 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>[웹] 연구 페이지 시각화: 이미지 15장 · 영상 재생 · 썸네일 · NEW 배지 · em dash 관문</t>
+          <t>[승격 검토] inbox/oh/20260814-pipeline-test.md</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
@@ -8917,20 +8887,20 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260814-pipeline-test.md</t>
+          <t>[작업] 자동 분류 배선 시험</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
@@ -8959,20 +8929,20 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>[작업] 자동 분류 배선 시험</t>
+          <t>[작업] 조선대 저장소 이력 소실 · 실습 zip 4종을 잃었다</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
@@ -9001,7 +8971,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>[작업] 조선대 저장소 이력 소실 · 실습 zip 4종을 잃었다</t>
+          <t>[작업] 강의 저장소 감시가 알림만 한다. 미러까지 하게</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -9014,7 +8984,7 @@
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -9043,20 +9013,20 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>[작업] 강의 저장소 감시가 알림만 한다. 미러까지 하게</t>
+          <t>[승격 검토] inbox/oh/20260831-runpod-환경구축.md</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
@@ -9085,20 +9055,20 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260831-runpod-환경구축.md</t>
+          <t>프로젝트 페이지 검색의 본문 색인 누락 (절 1500자 잘림)</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -9127,31 +9097,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>프로젝트 페이지 검색의 본문 색인 누락 (절 1500자 잘림)</t>
+          <t>[작업] AGENTS.md 와 docs/WORKFLOW.md 가 「코드를 어디에 올리나」를 다르게 적고 있다</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -9169,27 +9135,31 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>[작업] AGENTS.md 와 docs/WORKFLOW.md 가 「코드를 어디에 올리나」를 다르게 적고 있다</t>
+          <t>report-v1 의 검색 단추·바닥 도장 누락 해소와 완비 관문 예외 철회</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -9207,26 +9177,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>report-v1 의 검색 단추·바닥 도장 누락 해소와 완비 관문 예외 철회</t>
+          <t>[선행] 사이트 영상을 NAS 로 옮기고 웹은 그대로 보이게 (Vercel 무료 배포 저장소 10 GB 100 %)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9249,7 +9215,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>[선행] 사이트 영상을 NAS 로 옮기고 웹은 그대로 보이게 (Vercel 무료 배포 저장소 10 GB 100 %)</t>
+          <t>[설계] 세션·폴더·파이프라인을 한 공간으로: 공용 판 · 메모리 · 오케스트레이션 후보 + 지난 구조 회고</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -9287,14 +9253,14 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>[설계] 세션·폴더·파이프라인을 한 공간으로: 공용 판 · 메모리 · 오케스트레이션 후보 + 지난 구조 회고</t>
+          <t>[작업 목록] lead 남은 일과 놓치지 않을 약속 (10/13 기준 · 보고마다 점검)</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -9353,7 +9319,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>197%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9413,7 +9379,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>276%</t>
+          <t>318%</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9469,7 +9435,7 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
-          <t>350%</t>
+          <t>408%</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -9525,7 +9491,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>373%</t>
+          <t>436%</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -9585,7 +9551,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>373%</t>
+          <t>436%</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -9641,7 +9607,7 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>400%</t>
+          <t>470%</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -9701,7 +9667,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>400%</t>
+          <t>470%</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -9761,7 +9727,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>433%</t>
+          <t>511%</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9821,7 +9787,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>433%</t>
+          <t>511%</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -9881,7 +9847,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>700%</t>
+          <t>840%</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -9941,7 +9907,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>850%</t>
+          <t>1025%</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10001,7 +9967,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10061,7 +10027,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10117,7 +10083,7 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10173,7 +10139,7 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -10233,7 +10199,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>124%</t>
+          <t>139%</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -10293,7 +10259,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>136%</t>
+          <t>158%</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -10353,7 +10319,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>136%</t>
+          <t>158%</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -10413,7 +10379,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>136%</t>
+          <t>158%</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -10473,7 +10439,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>141%</t>
+          <t>166%</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -10533,7 +10499,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>141%</t>
+          <t>166%</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -10593,7 +10559,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>141%</t>
+          <t>166%</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -10653,7 +10619,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>144%</t>
+          <t>170%</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -10713,7 +10679,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>144%</t>
+          <t>170%</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -10773,7 +10739,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>157%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -10833,7 +10799,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>157%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -10893,7 +10859,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>157%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -10953,7 +10919,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>157%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -11013,7 +10979,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>157%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -11069,7 +11035,7 @@
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
-          <t>157%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -11125,7 +11091,7 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>157%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -11181,7 +11147,7 @@
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
-          <t>157%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -11237,7 +11203,7 @@
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
-          <t>157%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -11293,7 +11259,7 @@
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
-          <t>157%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -11353,7 +11319,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>157%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -11413,7 +11379,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>157%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -11473,7 +11439,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -11533,7 +11499,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -11593,7 +11559,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -11653,7 +11619,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -11713,7 +11679,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -11773,7 +11739,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -11833,7 +11799,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>175%</t>
+          <t>219%</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -11893,7 +11859,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>500%</t>
+          <t>733%</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -11953,7 +11919,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>1300%</t>
+          <t>2000%</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -12009,7 +11975,7 @@
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -12069,7 +12035,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>643%</t>
+          <t>743%</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -12129,7 +12095,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>643%</t>
+          <t>743%</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -12189,7 +12155,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>643%</t>
+          <t>743%</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -12249,7 +12215,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>643%</t>
+          <t>743%</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -12309,7 +12275,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>643%</t>
+          <t>743%</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -12369,7 +12335,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>643%</t>
+          <t>743%</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -12429,7 +12395,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>643%</t>
+          <t>743%</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -12489,7 +12455,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>643%</t>
+          <t>743%</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -12549,7 +12515,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>733%</t>
+          <t>850%</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -12609,7 +12575,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>1050%</t>
+          <t>1225%</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -12669,7 +12635,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>1050%</t>
+          <t>1225%</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -12729,7 +12695,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>1050%</t>
+          <t>1225%</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -12789,7 +12755,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>1367%</t>
+          <t>1600%</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -12849,7 +12815,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>1367%</t>
+          <t>1600%</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -12909,7 +12875,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>1367%</t>
+          <t>1600%</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -12969,7 +12935,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>3900%</t>
+          <t>4600%</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -13029,7 +12995,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>3900%</t>
+          <t>4600%</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -13089,7 +13055,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>3900%</t>
+          <t>4600%</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -16203,7 +16169,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>475%</t>
+          <t>562%</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -16263,7 +16229,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>475%</t>
+          <t>562%</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -16323,7 +16289,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>475%</t>
+          <t>562%</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -16383,7 +16349,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>475%</t>
+          <t>562%</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -16443,7 +16409,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>475%</t>
+          <t>562%</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -16503,7 +16469,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>850%</t>
+          <t>1025%</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -16563,7 +16529,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>850%</t>
+          <t>1025%</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -16623,7 +16589,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>1100%</t>
+          <t>1333%</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">

--- a/deliverables/plan/wbs.xlsx
+++ b/deliverables/plan/wbs.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -457,7 +457,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -725,40 +725,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[정책 학습]</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>32</v>
-      </c>
+          <t>TAGA(2606.05880) 지각 신경망 분석과 Go2 설계 적용 검토</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>219%</t>
-        </is>
-      </c>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -766,14 +748,10 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
@@ -785,7 +763,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 5종 담당을 정한다</t>
+          <t>[정책 학습]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -794,11 +772,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -808,12 +786,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>318%</t>
+          <t>242%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -833,7 +811,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
@@ -845,7 +823,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[작업] 레일즈 MuJoCo 사전 측정과 Isaac 스윕 설계</t>
+          <t>[작업] 실패 지형 5종 담당을 정한다</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -854,11 +832,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -868,12 +846,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>385%</t>
+          <t>359%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -883,7 +861,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -905,7 +883,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[작업] RunPod에서 Isaac 험지 지형 headless 생성·확인 환경 확보</t>
+          <t>[작업] 레일즈 MuJoCo 사전 측정과 Isaac 스윕 설계</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -914,11 +892,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -928,12 +906,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>408%</t>
+          <t>438%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -943,7 +921,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -965,7 +943,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[작업] 험지 지형 종류 확장 및 난이도 파라미터화</t>
+          <t>[작업] RunPod에서 Isaac 험지 지형 headless 생성·확인 환경 확보</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -993,7 +971,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>408%</t>
+          <t>467%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1025,7 +1003,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[작업] 평지 직진 기준선 수립 + 미경험 10종 동일 조건 재측정</t>
+          <t>[작업] 험지 지형 종류 확장 및 난이도 파라미터화</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1034,11 +1012,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1048,12 +1026,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>436%</t>
+          <t>467%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1063,7 +1041,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1085,7 +1063,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[작업] 기본 지형 6종에 대해서 정책 개선</t>
+          <t>[작업] 평지 직진 기준선 수립 + 미경험 10종 동일 조건 재측정</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1094,32 +1072,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>511%</t>
+          <t>500%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>IQ152</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1141,7 +1123,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[작업] NVIDA checkpoint 기본 성능 분석 및 추가 학습 설계 분석</t>
+          <t>[작업] 기본 지형 6종에 대해서 정책 개선</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1150,11 +1132,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1162,19 +1144,15 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>562%</t>
+          <t>589%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1201,7 +1179,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[계획] 발 높이의 상수에서 명령으로의 전환 설계</t>
+          <t>[작업] NVIDA checkpoint 기본 성능 분석 및 추가 학습 설계 분석</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1210,26 +1188,26 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>840%</t>
+          <t>650%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1239,7 +1217,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1261,7 +1239,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[작업] 레일즈 학습 레시피 한 장으로 모으기</t>
+          <t>[계획] 발 높이의 상수에서 명령으로의 전환 설계</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1270,11 +1248,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1284,12 +1262,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1950%</t>
+          <t>980%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1299,7 +1277,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1321,7 +1299,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[계획] 실패 지형 공략 뼈대의 N차 누적 전환과 연구 보드 축 재구성</t>
+          <t>[작업] 레일즈 학습 레시피 한 장으로 모으기</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1330,24 +1308,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2300%</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>100%</t>
@@ -1355,7 +1337,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1377,7 +1359,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[작업] E 정책 비교 영상 13종 촬영</t>
+          <t>[계획] 실패 지형 공략 뼈대의 N차 누적 전환과 연구 보드 축 재구성</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1386,11 +1368,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1433,37 +1415,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[작업] 테스트</t>
+          <t>[작업] E 정책 비교 영상 13종 촬영</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>A-정책</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>35</v>
+        <v>-6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>156%</t>
-        </is>
-      </c>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>100%</t>
@@ -1471,12 +1449,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/midterm/policy-metrics.md</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1493,7 +1471,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 gap: 진단 -&gt; 레시피 (임석헌)</t>
+          <t>[작업] 테스트</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1502,11 +1480,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1516,12 +1494,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>158%</t>
+          <t>176%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1531,7 +1509,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>IQ152</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1553,7 +1531,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 rails: 진단 -&gt; 레시피 (맹라현)</t>
+          <t>[작업] 실패 지형 gap: 진단 -&gt; 레시피 (임석헌)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1581,7 +1559,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>158%</t>
+          <t>179%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1591,7 +1569,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1613,7 +1591,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 stepping_stones: 진단 -&gt; 레시피 (오현민)</t>
+          <t>[작업] 실패 지형 rails: 진단 -&gt; 레시피 (맹라현)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1641,7 +1619,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>158%</t>
+          <t>179%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1651,7 +1629,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1673,7 +1651,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 pit: 진단 -&gt; 레시피 (이민우)</t>
+          <t>[작업] 실패 지형 stepping_stones: 진단 -&gt; 레시피 (오현민)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1701,7 +1679,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>158%</t>
+          <t>179%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1711,7 +1689,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>lmw0207</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1733,7 +1711,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[작업] 실패 지형 floating_ring: 진단 -&gt; 레시피 (오흥재)</t>
+          <t>[작업] 실패 지형 pit: 진단 -&gt; 레시피 (이민우)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1761,7 +1739,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>158%</t>
+          <t>179%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1771,7 +1749,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>lmw0207</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1793,7 +1771,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Go2 관절 각도 한계 기구학 계산 (5 cm 벽)</t>
+          <t>[작업] 실패 지형 floating_ring: 진단 -&gt; 레시피 (오흥재)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1802,11 +1780,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1821,7 +1799,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>166%</t>
+          <t>179%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1853,7 +1831,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[리서치] 학습 보상에 발 높이 항이 없다는 확인</t>
+          <t>Go2 관절 각도 한계 기구학 계산 (5 cm 벽)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1862,11 +1840,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1876,12 +1854,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>173%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1891,7 +1869,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1913,7 +1891,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[리서치] 레일 통과와 보상 설계: 외부 문헌 여섯 편 대조</t>
+          <t>[리서치] 학습 보상에 발 높이 항이 없다는 확인</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1922,11 +1900,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1934,15 +1912,19 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>179%</t>
+          <t>200%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1969,7 +1951,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[작업] RL gap 30cm 범위까지 추가 학습 및 검증</t>
+          <t>[리서치] 레일 통과와 보상 설계: 외부 문헌 여섯 편 대조</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1978,11 +1960,11 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1993,7 +1975,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>195%</t>
+          <t>208%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2003,7 +1985,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>IQ152</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2025,7 +2007,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[작업] foothold-v1.pt에서 rails 지형 추가 학습</t>
+          <t>[작업] RL gap 30cm 범위까지 추가 학습 및 검증</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2034,11 +2016,11 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2046,19 +2028,15 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>230%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2085,7 +2063,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[작업] 500 iter 실행 기록 복원 · 레시피 중간 단계</t>
+          <t>[작업] foothold-v1.pt에서 rails 지형 추가 학습</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2094,11 +2072,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2108,12 +2086,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>227%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2123,7 +2101,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2145,7 +2123,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[작업] 레시피 계보 기록 · A·B 출발점과 설정 diff</t>
+          <t>[작업] 500 iter 실행 기록 복원 · 레시피 중간 단계</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2173,7 +2151,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>227%</t>
+          <t>273%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2205,7 +2183,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[작업] 명령 능력 복원 D 학습 · 정지·저속·회전 프로브 신설과 기준선 측정</t>
+          <t>[작업] 레시피 계보 기록 · A·B 출발점과 설정 diff</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2214,11 +2192,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2233,7 +2211,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>258%</t>
+          <t>273%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2265,7 +2243,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[작업] E 환경 설정과 Isaac Lab 등록</t>
+          <t>[작업] 명령 능력 복원 D 학습 · 정지·저속·회전 프로브 신설과 기준선 측정</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2274,11 +2252,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2293,7 +2271,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>273%</t>
+          <t>317%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2325,7 +2303,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[조사] 지각 논문 MARG · HiPAN · AME-2 정밀 검토</t>
+          <t>[작업] E 환경 설정과 Isaac Lab 등록</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2334,11 +2312,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2353,7 +2331,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>311%</t>
+          <t>336%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2385,7 +2363,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[계획] 험지 통과와 기본 명령을 함께 학습하는 연구 방향 정리</t>
+          <t>[조사] 지각 논문 MARG · HiPAN · AME-2 정밀 검토</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2394,11 +2372,11 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2408,12 +2386,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2000%</t>
+          <t>389%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2440,40 +2418,40 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A2 지형·씬 제작</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[작업] MuJoCo ↔ Isaac Sim 관측 차원 차이 조사: 결과를 어디까지 근거로 쓸 것인가</t>
+          <t>[계획] 험지 통과와 기본 명령을 함께 학습하는 연구 방향 정리</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>436%</t>
+          <t>2700%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2488,7 +2466,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2500,55 +2478,51 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A2 지형·씬 제작</t>
+          <t>A1 정책 학습</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[작업] 파인튜닝 가능한 지형 조사</t>
+          <t>[작업] 마찰 도메인 무작위화 미실행 축 기록 + 적용 시 함정 셋 (make_consistent · 지형 대 로봇 재질 · 저속 커리큘럼)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>NAV · 실기 항법</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>156%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/final/nav-report.md</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2560,28 +2534,42 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A3 평가</t>
+          <t>A2 지형·씬 제작</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[실측] WS: DDP 판정 · 1,500 완주 · 평가 기준선 86.7% · 난이도 곡선</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+          <t>[작업] MuJoCo ↔ Isaac Sim 관측 차원 차이 조사: 결과를 어디까지 근거로 쓸 것인가</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>500%</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>100%</t>
@@ -2592,7 +2580,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2602,28 +2594,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A3 평가</t>
+          <t>A2 지형·씬 제작</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/lim/20260822-베이스라인 모델의 간단한 미경험 험지 성능 측정.md</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+          <t>[작업] 파인튜닝 가능한 지형 조사</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MVP · 중간발표</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>35</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>176%</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>100%</t>
@@ -2631,10 +2637,14 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>maengu86</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/generalization-report.md</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2649,37 +2659,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[작업] RoboGauge 공개 정책 4종: 우리 평가에 붙이기</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>A-정책</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>32</v>
-      </c>
+          <t>[승격 검토] inbox/lim/20260822-베이스라인 모델의 간단한 미경험 험지 성능 측정.md</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>219%</t>
-        </is>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>100%</t>
@@ -2687,14 +2683,10 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>vfxpedia,less82</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
-        </is>
-      </c>
+          <t>vfxpedia</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -2737,7 +2729,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>436%</t>
+          <t>500%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2797,7 +2789,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>436%</t>
+          <t>500%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2857,7 +2849,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>436%</t>
+          <t>500%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2917,7 +2909,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>470%</t>
+          <t>540%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2977,7 +2969,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>511%</t>
+          <t>589%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3037,7 +3029,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>562%</t>
+          <t>650%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3097,7 +3089,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1025%</t>
+          <t>1200%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3153,7 +3145,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1025%</t>
+          <t>1200%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3213,7 +3205,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1025%</t>
+          <t>1200%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3269,7 +3261,7 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1025%</t>
+          <t>1200%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3325,7 +3317,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1025%</t>
+          <t>1200%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3381,7 +3373,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1025%</t>
+          <t>1200%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3437,7 +3429,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1025%</t>
+          <t>1200%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3497,7 +3489,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1025%</t>
+          <t>1200%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3557,7 +3549,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1025%</t>
+          <t>1200%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3617,7 +3609,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1333%</t>
+          <t>1567%</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3673,7 +3665,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1333%</t>
+          <t>1567%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3733,7 +3725,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1333%</t>
+          <t>1567%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3793,7 +3785,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1333%</t>
+          <t>1567%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3853,7 +3845,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>139%</t>
+          <t>153%</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3913,7 +3905,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>170%</t>
+          <t>196%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3973,7 +3965,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>186%</t>
+          <t>218%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4033,7 +4025,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>186%</t>
+          <t>218%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4089,7 +4081,7 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>190%</t>
+          <t>224%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4149,7 +4141,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>200%</t>
+          <t>237%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4209,7 +4201,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>200%</t>
+          <t>237%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4269,7 +4261,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>200%</t>
+          <t>237%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4329,7 +4321,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>200%</t>
+          <t>237%</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4389,7 +4381,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>236%</t>
+          <t>286%</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4445,7 +4437,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>258%</t>
+          <t>317%</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4505,7 +4497,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>371%</t>
+          <t>471%</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4561,7 +4553,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>371%</t>
+          <t>471%</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4621,7 +4613,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>417%</t>
+          <t>533%</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4681,7 +4673,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>417%</t>
+          <t>533%</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4741,7 +4733,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>417%</t>
+          <t>533%</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4801,7 +4793,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>733%</t>
+          <t>967%</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4861,7 +4853,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>733%</t>
+          <t>967%</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4917,7 +4909,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>733%</t>
+          <t>967%</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4977,7 +4969,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1050%</t>
+          <t>1400%</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5037,7 +5029,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4600%</t>
+          <t>5300%</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5097,7 +5089,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4600%</t>
+          <t>5300%</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5233,7 +5225,7 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5293,7 +5285,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>139%</t>
+          <t>153%</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5353,7 +5345,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>236%</t>
+          <t>286%</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5413,7 +5405,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>236%</t>
+          <t>286%</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5473,7 +5465,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>236%</t>
+          <t>286%</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5735,7 +5727,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5791,7 +5783,7 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5851,7 +5843,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5907,7 +5899,7 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6295,7 +6287,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>242%</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6355,7 +6347,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>318%</t>
+          <t>359%</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6415,7 +6407,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>436%</t>
+          <t>500%</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6475,7 +6467,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>436%</t>
+          <t>500%</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6535,7 +6527,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>511%</t>
+          <t>589%</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6595,7 +6587,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>562%</t>
+          <t>650%</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6655,7 +6647,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1333%</t>
+          <t>1567%</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6715,7 +6707,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6775,7 +6767,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>158%</t>
+          <t>179%</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6835,7 +6827,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>158%</t>
+          <t>179%</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -6895,7 +6887,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>158%</t>
+          <t>179%</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6955,7 +6947,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>158%</t>
+          <t>179%</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7015,7 +7007,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>166%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7075,7 +7067,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>166%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7135,7 +7127,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>190%</t>
+          <t>224%</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7195,7 +7187,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7255,7 +7247,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7315,7 +7307,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7375,7 +7367,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7435,7 +7427,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7495,7 +7487,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7555,7 +7547,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7615,7 +7607,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7675,7 +7667,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>227%</t>
+          <t>273%</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7735,7 +7727,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2000%</t>
+          <t>2700%</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7795,7 +7787,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2000%</t>
+          <t>2700%</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7855,7 +7847,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2000%</t>
+          <t>2700%</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7915,7 +7907,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2000%</t>
+          <t>2700%</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8027,7 +8019,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8087,7 +8079,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>1600%</t>
+          <t>1833%</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8147,7 +8139,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>1600%</t>
+          <t>1833%</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8207,7 +8199,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>1600%</t>
+          <t>1833%</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8267,7 +8259,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>1600%</t>
+          <t>1833%</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8327,7 +8319,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>1600%</t>
+          <t>1833%</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8387,7 +8379,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>1600%</t>
+          <t>1833%</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8447,7 +8439,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>4600%</t>
+          <t>5300%</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8507,7 +8499,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>4600%</t>
+          <t>5300%</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8567,7 +8559,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>4600%</t>
+          <t>5300%</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8627,7 +8619,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>4600%</t>
+          <t>5300%</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8687,7 +8679,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>4600%</t>
+          <t>5300%</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -8761,20 +8753,20 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>[테스트] 루프 차단 후 sub-issue 재검증</t>
+          <t>[승격 검토] inbox/oh/20260814-pipeline-test.md</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -8803,20 +8795,20 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>[웹] 연구 페이지 시각화: 이미지 15장 · 영상 재생 · 썸네일 · NEW 배지 · em dash 관문</t>
+          <t>[작업] 자동 분류 배선 시험</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -8845,20 +8837,20 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260814-pipeline-test.md</t>
+          <t>[작업] 조선대 저장소 이력 소실 · 실습 zip 4종을 잃었다</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
@@ -8887,20 +8879,20 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>[작업] 자동 분류 배선 시험</t>
+          <t>[작업] 강의 저장소 감시가 알림만 한다. 미러까지 하게</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
@@ -8929,20 +8921,20 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>[작업] 조선대 저장소 이력 소실 · 실습 zip 4종을 잃었다</t>
+          <t>[승격 검토] inbox/oh/20260831-runpod-환경구축.md</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
@@ -8971,14 +8963,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>[작업] 강의 저장소 감시가 알림만 한다. 미러까지 하게</t>
+          <t>프로젝트 페이지 검색의 본문 색인 누락 (절 1500자 잘림)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -9013,31 +9005,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260831-runpod-환경구축.md</t>
+          <t>[작업] AGENTS.md 와 docs/WORKFLOW.md 가 「코드를 어디에 올리나」를 다르게 적고 있다</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9055,14 +9043,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>프로젝트 페이지 검색의 본문 색인 누락 (절 1500자 잘림)</t>
+          <t>report-v1 의 검색 단추·바닥 도장 누락 해소와 완비 관문 예외 철회</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -9097,14 +9085,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>[작업] AGENTS.md 와 docs/WORKFLOW.md 가 「코드를 어디에 올리나」를 다르게 적고 있다</t>
+          <t>[선행] 사이트 영상을 NAS 로 옮기고 웹은 그대로 보이게 (Vercel 무료 배포 저장소 10 GB 100 %)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -9117,7 +9105,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -9135,26 +9123,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>report-v1 의 검색 단추·바닥 도장 누락 해소와 완비 관문 예외 철회</t>
+          <t>[설계] 세션·폴더·파이프라인을 한 공간으로: 공용 판 · 메모리 · 오케스트레이션 후보 + 지난 구조 회고</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9177,14 +9161,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>[선행] 사이트 영상을 NAS 로 옮기고 웹은 그대로 보이게 (Vercel 무료 배포 저장소 10 GB 100 %)</t>
+          <t>[작업 목록] lead 남은 일과 놓치지 않을 약속 (10/13 기준 · 보고마다 점검)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -9215,22 +9199,40 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>[설계] 세션·폴더·파이프라인을 한 공간으로: 공용 판 · 메모리 · 오케스트레이션 후보 + 지난 구조 회고</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
+          <t>[인프라] Vaultwarden 개통 + NAS 폴더 구조</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>32</v>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>242%</t>
+        </is>
+      </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9238,7 +9240,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -9253,22 +9259,40 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>[작업 목록] lead 남은 일과 놓치지 않을 약속 (10/13 기준 · 보고마다 점검)</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
+          <t>[작업] 자동 분류 배선 시험 2</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>A-정책</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>18</v>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>359%</t>
+        </is>
+      </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9276,7 +9300,11 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>deliverables/midterm/policy-metrics.md</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -9291,7 +9319,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>[인프라] Vaultwarden 개통 + NAS 폴더 구조</t>
+          <t>[작업] RunPod 네트워크 볼륨 개설과 팀 폴더 구조 표준화</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9300,11 +9328,11 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -9312,26 +9340,18 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>467%</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
           <t>deliverables/midterm/policy-metrics.md</t>
@@ -9351,7 +9371,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>[작업] 자동 분류 배선 시험 2</t>
+          <t>[작업] 맹 개인 규정 v2.4: 작업 자리를 저장소 밖으로 옮긴다</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9360,11 +9380,11 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -9374,12 +9394,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>318%</t>
+          <t>500%</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9389,7 +9409,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -9411,7 +9431,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>[작업] RunPod 네트워크 볼륨 개설과 팀 폴더 구조 표준화</t>
+          <t>[작업] 맹 개인 규정 v2.5: 이슈를 열면 바로 In Progress 로 잡는다</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9420,11 +9440,11 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -9432,18 +9452,26 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>408%</t>
+          <t>500%</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr"/>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>maengu86</t>
+        </is>
+      </c>
       <c r="K165" t="inlineStr">
         <is>
           <t>deliverables/midterm/policy-metrics.md</t>
@@ -9463,7 +9491,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>[작업] 맹 개인 규정 v2.4: 작업 자리를 저장소 밖으로 옮긴다</t>
+          <t>저장소 역할 재정의를 운영 문서에 반영 (lab 개발 · go2 공개 승격)</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9472,11 +9500,11 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -9484,24 +9512,20 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>436%</t>
+          <t>540%</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -9523,7 +9547,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>[작업] 맹 개인 규정 v2.5: 이슈를 열면 바로 In Progress 로 잡는다</t>
+          <t>실험 템플릿 lab 이관과 「승격」 용어 분리 (저장소 재정의 여파)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9532,11 +9556,11 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -9546,12 +9570,12 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>436%</t>
+          <t>540%</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -9561,7 +9585,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -9583,7 +9607,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>저장소 역할 재정의를 운영 문서에 반영 (lab 개발 · go2 공개 승격)</t>
+          <t>[작업] 연구 허브 Track A 실패 험지 5종 카드 절 신설</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9592,11 +9616,11 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -9604,15 +9628,19 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>470%</t>
+          <t>589%</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9639,7 +9667,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>실험 템플릿 lab 이관과 「승격」 용어 분리 (저장소 재정의 여파)</t>
+          <t>[작업] 연구 허브 험지 카드 후속 과제 중복 제거 · 5열 배치 · 칩 작성자 시각 표기 · 미분류 8건 분류</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9648,11 +9676,11 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -9667,7 +9695,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>470%</t>
+          <t>589%</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -9699,7 +9727,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>[작업] 연구 허브 Track A 실패 험지 5종 카드 절 신설</t>
+          <t>[작업] 원장 전수 절 동기화 · 닫힌 7건 정리와 새 6건 반영</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9708,11 +9736,11 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -9722,12 +9750,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>511%</t>
+          <t>980%</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9759,7 +9787,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>[작업] 연구 허브 험지 카드 후속 과제 중복 제거 · 5열 배치 · 칩 작성자 시각 표기 · 미분류 8건 분류</t>
+          <t>[작업] 워크플로 15군데 em dash 정리와 관문 확장</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -9768,11 +9796,11 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -9787,7 +9815,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>511%</t>
+          <t>1200%</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -9819,35 +9847,35 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>[작업] 원장 전수 절 동기화 · 닫힌 7건 정리와 새 6건 반영</t>
+          <t>[운영]</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>FINAL · 최종발표</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>6</v>
+        <v>118</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>840%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -9862,12 +9890,12 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/final/final-report.md</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>foothold-lab</t>
+          <t>foothold-go2</t>
         </is>
       </c>
     </row>
@@ -9879,25 +9907,25 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>[작업] 워크플로 15군데 em dash 정리와 관문 확장</t>
+          <t>[작업] ledger-sync 경고 줄로 인한 GITHUB_OUTPUT 형식 오류 수정과 디스코드 닫힘 알림 문구 구분</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>A-정책</t>
+          <t>FINAL · 최종발표</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -9907,7 +9935,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>1025%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -9922,7 +9950,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>deliverables/midterm/policy-metrics.md</t>
+          <t>deliverables/final/final-report.md</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -9939,7 +9967,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>[운영]</t>
+          <t>[작업] 브랜드 관문 유예 명부의 조용한 기준선 재설정 차단과 공통 틀 위반 상환</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9948,11 +9976,11 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -9960,19 +9988,15 @@
           <t>2026-12-07</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -9987,7 +10011,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>foothold-go2</t>
+          <t>foothold-lab</t>
         </is>
       </c>
     </row>
@@ -9999,7 +10023,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>[작업] ledger-sync 경고 줄로 인한 GITHUB_OUTPUT 형식 오류 수정과 디스코드 닫힘 알림 문구 구분</t>
+          <t>[계획] MVP 이후 설계 논의 · 팀원 보고의 하나의 흐름 · 방향 점검 · RL Top-down</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10008,11 +10032,11 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -10020,19 +10044,15 @@
           <t>2026-12-07</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10059,36 +10079,40 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>[작업] 브랜드 관문 유예 명부의 조용한 기준선 재설정 차단과 공통 틀 위반 상환</t>
+          <t>[작업] 우분투 전환 후 DDP 재측정</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>FINAL · 최종발표</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>153%</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10098,7 +10122,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>deliverables/final/final-report.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10115,36 +10139,40 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>[계획] MVP 이후 설계 논의 · 팀원 보고의 하나의 흐름 · 방향 점검 · RL Top-down</t>
+          <t>[작업] 일정 시스템 구현 (8/26 설계안이 통째로 증발했다)</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>FINAL · 최종발표</t>
+          <t>MVP · 중간발표</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr"/>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>179%</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10154,7 +10182,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>deliverables/final/final-report.md</t>
+          <t>deliverables/midterm/generalization-report.md</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -10171,7 +10199,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>[작업] 우분투 전환 후 DDP 재측정</t>
+          <t>[작업] NEW 배지가 허브에서는 안 뜬다 (설계 재정비)</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10180,11 +10208,11 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -10194,12 +10222,12 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>139%</t>
+          <t>179%</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -10231,7 +10259,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>[작업] 일정 시스템 구현 (8/26 설계안이 통째로 증발했다)</t>
+          <t>[작업] 브랜드·테마 일관성: 전역바 로고가 정본이 아니다</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10254,12 +10282,12 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>158%</t>
+          <t>179%</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -10291,7 +10319,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>[작업] NEW 배지가 허브에서는 안 뜬다 (설계 재정비)</t>
+          <t>웹 문서에 출처 이슈 표기</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10300,11 +10328,11 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -10314,12 +10342,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>158%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -10351,7 +10379,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>[작업] 브랜드·테마 일관성: 전역바 로고가 정본이 아니다</t>
+          <t>판 번호 자동 갱신</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10360,11 +10388,11 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -10379,7 +10407,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>158%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -10411,7 +10439,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>웹 문서에 출처 이슈 표기</t>
+          <t>공개 문서 금액 표기 정정과 redact 금액 탐지 개선</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10439,7 +10467,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>166%</t>
+          <t>190%</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -10471,7 +10499,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>판 번호 자동 갱신</t>
+          <t>[작업] 빌드 실행 순서 결함 2건 수정과 생성물 커밋·정상 배포</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10480,11 +10508,11 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -10494,12 +10522,12 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>166%</t>
+          <t>196%</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -10531,7 +10559,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>공개 문서 금액 표기 정정과 redact 금액 탐지 개선</t>
+          <t>[작업] LEDGER 열린 이슈 전수 자동 집계와 원장 반영</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10540,11 +10568,11 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10554,12 +10582,12 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>166%</t>
+          <t>196%</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -10591,7 +10619,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>[작업] 빌드 실행 순서 결함 2건 수정과 생성물 커밋·정상 배포</t>
+          <t>원장 관문 [3.8] 과 ledger-sync 봇의 경합으로 인한 배포 중단</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10600,11 +10628,11 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10619,7 +10647,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>170%</t>
+          <t>224%</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -10651,7 +10679,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>[작업] LEDGER 열린 이슈 전수 자동 집계와 원장 반영</t>
+          <t>코드블록 위젯 CSS 의 토큰 밖 색상 19개 · 배포본 130장 공통</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10660,11 +10688,11 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10674,12 +10702,12 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>170%</t>
+          <t>224%</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -10711,7 +10739,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>원장 관문 [3.8] 과 ledger-sync 봇의 경합으로 인한 배포 중단</t>
+          <t>[작업] 팀 제출·완결 조건의 문서화 · 개인 위키 게재의 지위 정리</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10739,7 +10767,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>190%</t>
+          <t>224%</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -10771,7 +10799,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>코드블록 위젯 CSS 의 토큰 밖 색상 19개 · 배포본 130장 공통</t>
+          <t>[작업] 관문 코드에만 사는 웹·운영 규칙 넷의 문서 이관</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10799,7 +10827,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>190%</t>
+          <t>224%</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -10831,7 +10859,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>[작업] 팀 제출·완결 조건의 문서화 · 개인 위키 게재의 지위 정리</t>
+          <t>배포본 diff 에서 빌드 시각을 걷어낸 «진짜 변경» 수 표시</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -10859,7 +10887,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>190%</t>
+          <t>224%</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -10891,7 +10919,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>[작업] 관문 코드에만 사는 웹·운영 규칙 넷의 문서 이관</t>
+          <t>[작업] deadline-alert.yml 보드 조회의 쪽 나눔과 훑은 건수 표기</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -10912,19 +10940,15 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
-          <t>190%</t>
+          <t>224%</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -10951,7 +10975,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>배포본 diff 에서 빌드 시각을 걷어낸 «진짜 변경» 수 표시</t>
+          <t>[작업] weekly-report.yml 의 전송 판정·쪽 나눔·바이트 자르기·상수 output 정리</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -10972,19 +10996,15 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
-          <t>190%</t>
+          <t>224%</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11011,7 +11031,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>[작업] deadline-alert.yml 보드 조회의 쪽 나눔과 훑은 건수 표기</t>
+          <t>[작업] lecture-watch.yml 스냅샷 저장 시점의 알림 뒤 이동</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11035,7 +11055,7 @@
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
-          <t>190%</t>
+          <t>224%</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -11067,7 +11087,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>[작업] weekly-report.yml 의 전송 판정·쪽 나눔·바이트 자르기·상수 output 정리</t>
+          <t>[작업] issue-dates.yml 필드 id 미확보 시 성공 표기 차단</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11091,7 +11111,7 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>190%</t>
+          <t>224%</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -11123,7 +11143,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>[작업] lecture-watch.yml 스냅샷 저장 시점의 알림 뒤 이동</t>
+          <t>[작업] merge-on-comment.yml 텔레그램 HTTP 코드 판정 추가</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11147,7 +11167,7 @@
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
-          <t>190%</t>
+          <t>224%</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -11179,7 +11199,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>[작업] issue-dates.yml 필드 id 미확보 시 성공 표기 차단</t>
+          <t>[작업] notice.yml 한글 공지의 글자 단위 분할</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11200,15 +11220,19 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>190%</t>
+          <t>224%</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11235,7 +11259,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>[작업] merge-on-comment.yml 텔레그램 HTTP 코드 판정 추가</t>
+          <t>[작업] authorcheck.py 의 ROLES.md 부재 시 진단문 유실</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11256,15 +11280,19 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>190%</t>
+          <t>224%</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11291,7 +11319,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>[작업] notice.yml 한글 공지의 글자 단위 분할</t>
+          <t>[작업] 주간 다이제스트 2주 밀림 해소와 cron 밀림 내성 확보</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11300,11 +11328,11 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -11314,12 +11342,12 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>190%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -11351,7 +11379,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>[작업] authorcheck.py 의 ROLES.md 부재 시 진단문 유실</t>
+          <t>[작업] 빌드 입력 트리 단일화 · _lab-main 후보 제거와 전수 순회 자리 정리</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11360,11 +11388,11 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -11379,7 +11407,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>190%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -11411,7 +11439,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>[작업] 주간 다이제스트 2주 밀림 해소와 cron 밀림 내성 확보</t>
+          <t>[작업] 폰에서 표가 짜부라지는 결함의 세 원인과 규칙 일원화</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11434,12 +11462,12 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -11471,7 +11499,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>[작업] 빌드 입력 트리 단일화 · _lab-main 후보 제거와 전수 순회 자리 정리</t>
+          <t>[작업] --repro 없는 --out 이 조용히 무시되고 실제 배포본에 쓰는 문제</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -11494,12 +11522,12 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -11531,7 +11559,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>[작업] 폰에서 표가 짜부라지는 결함의 세 원인과 규칙 일원화</t>
+          <t>[작업] 연구 허브 카드가 날짜로 정렬되지 않는 문제 (자리 둘 다)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -11559,7 +11587,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -11591,7 +11619,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>[작업] --repro 없는 --out 이 조용히 무시되고 실제 배포본에 쓰는 문제</t>
+          <t>[작업] 배포본 영상 19개에 썸네일 부재 · 프레임 0 이 전부 검정</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -11619,7 +11647,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -11651,7 +11679,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>[작업] 연구 허브 카드가 날짜로 정렬되지 않는 문제 (자리 둘 다)</t>
+          <t>[작업] 마크다운 문법이 글자로 보이는 자리 29곳 · h5·h6 미지원과 인용·카드</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -11679,7 +11707,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>262%</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -11711,7 +11739,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>[작업] 배포본 영상 19개에 썸네일 부재 · 프레임 0 이 전부 검정</t>
+          <t>[운영] RL 결과를 연구 페이지 두 장으로 · 웹 관문 셋 해제</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11720,11 +11748,11 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -11734,12 +11762,12 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>967%</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -11771,7 +11799,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>[작업] 마크다운 문법이 글자로 보이는 자리 29곳 · h5·h6 미지원과 인용·카드</t>
+          <t>[작업] Astra 검증 적용 범위 및 반복 기준 조정</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -11780,11 +11808,11 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -11794,12 +11822,12 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>219%</t>
+          <t>2700%</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -11831,40 +11859,36 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>[운영] RL 결과를 연구 페이지 두 장으로 · 웹 관문 셋 해제</t>
+          <t>[작업] 압축 직전 인계 훅의 프로젝트 설정 이관</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>NAV · 실기 항법</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
-          <t>733%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -11874,7 +11898,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/final/nav-report.md</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -11891,35 +11915,35 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>[작업] Astra 검증 적용 범위 및 반복 기준 조정</t>
+          <t>[작업] WBS 자동 생성 결과가 웹에 도달하지 않는다</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>MVP · 중간발표</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2000%</t>
+          <t>843%</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -11934,7 +11958,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>deliverables/midterm/generalization-report.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -11951,46 +11975,50 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>[작업] 압축 직전 인계 훅의 프로젝트 설정 이관</t>
+          <t>[주간] W35 팀 목표 (8/24~8/30)</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>NAV · 실기 항법</t>
+          <t>기획발표</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>843%</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>vfxpedia,less82,lmw0207,IQ152,maengu86</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>deliverables/final/nav-report.md</t>
+          <t>deliverables/plan/wbs.md</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -12007,7 +12035,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>[작업] WBS 자동 생성 결과가 웹에 도달하지 않는다</t>
+          <t>[주간] W36 팀 목표 (8/31~9/6) · 기획발표 주</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12030,12 +12058,12 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>743%</t>
+          <t>843%</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -12045,7 +12073,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>vfxpedia,less82,lmw0207,IQ152,maengu86</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -12067,7 +12095,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>[주간] W35 팀 목표 (8/24~8/30)</t>
+          <t>[주간] W36 오흥재 개인 목표</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12095,7 +12123,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>743%</t>
+          <t>843%</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -12105,7 +12133,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>vfxpedia,less82,lmw0207,IQ152,maengu86</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -12127,7 +12155,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>[주간] W36 팀 목표 (8/31~9/6) · 기획발표 주</t>
+          <t>[주간] W36 맹라현 개인 목표</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12155,7 +12183,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>743%</t>
+          <t>843%</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -12165,7 +12193,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>vfxpedia,less82,lmw0207,IQ152,maengu86</t>
+          <t>maengu86</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -12187,7 +12215,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>[주간] W36 오흥재 개인 목표</t>
+          <t>[주간] W36 오현민 개인 목표</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12215,7 +12243,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>743%</t>
+          <t>843%</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -12225,7 +12253,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>less82</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -12247,7 +12275,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>[주간] W36 맹라현 개인 목표</t>
+          <t>[주간] W36 임석헌 개인 목표</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -12275,7 +12303,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>743%</t>
+          <t>843%</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -12285,7 +12313,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>maengu86</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -12307,7 +12335,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>[주간] W36 오현민 개인 목표</t>
+          <t>[주간] W36 이민우 개인 목표</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -12335,7 +12363,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>743%</t>
+          <t>843%</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -12345,7 +12373,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>less82</t>
+          <t>lmw0207</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -12367,7 +12395,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>[주간] W36 임석헌 개인 목표</t>
+          <t>[작업] v2.0.0 적용 완료 점검 · 여덟 가지를 실측으로 확인한다</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -12376,11 +12404,11 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -12395,7 +12423,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>743%</t>
+          <t>967%</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -12405,7 +12433,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>IQ152</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -12427,7 +12455,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>[주간] W36 이민우 개인 목표</t>
+          <t>[작업] PRD-WEB 정렬 패스 · 기준 한 장대로 전 화면을 맞춘다</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -12436,11 +12464,11 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -12455,7 +12483,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>743%</t>
+          <t>1400%</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -12465,7 +12493,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>lmw0207</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -12487,7 +12515,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>[작업] v2.0.0 적용 완료 점검 · 여덟 가지를 실측으로 확인한다</t>
+          <t>[작업] 표지를 타겟 기준으로 재구성 · 온톨로지의 마지막 축을 쓴다</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -12496,11 +12524,11 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -12515,7 +12543,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>850%</t>
+          <t>1400%</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -12547,7 +12575,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>[작업] PRD-WEB 정렬 패스 · 기준 한 장대로 전 화면을 맞춘다</t>
+          <t>[작업] 멘토링 질문 사전 취합 · 노션 설계안의 빠진 조각</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -12575,7 +12603,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>1225%</t>
+          <t>1400%</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -12607,7 +12635,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>[작업] 표지를 타겟 기준으로 재구성 · 온톨로지의 마지막 축을 쓴다</t>
+          <t>[작업] 오늘 하루 진행 관리: 이슈 상태를 In Progress 로 유지하며 작업</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -12616,11 +12644,11 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -12635,7 +12663,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>1225%</t>
+          <t>1833%</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -12667,7 +12695,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>[작업] 멘토링 질문 사전 취합 · 노션 설계안의 빠진 조각</t>
+          <t>웹 v2.0.0 확정과 공지</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -12676,11 +12704,11 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -12695,7 +12723,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>1225%</t>
+          <t>1833%</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -12727,7 +12755,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>[작업] 오늘 하루 진행 관리: 이슈 상태를 In Progress 로 유지하며 작업</t>
+          <t>WBS 구현 단계 층 신설과 사람별 기여 축</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -12755,7 +12783,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>1600%</t>
+          <t>1833%</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -12787,7 +12815,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>웹 v2.0.0 확정과 공지</t>
+          <t>[작업] 표지 D-day 계산 결함 수정 · 경과 시간 기준을 KST 달력 날짜 차이로 교정</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -12796,11 +12824,11 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -12810,12 +12838,12 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>1600%</t>
+          <t>5300%</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -12847,7 +12875,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>WBS 구현 단계 층 신설과 사람별 기여 축</t>
+          <t>[작업] 일정 허브 멘토링 D-day 주간 반복 반영 · 빌드 시점 고정값 제거</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -12856,11 +12884,11 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -12875,7 +12903,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>1600%</t>
+          <t>5300%</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -12907,7 +12935,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>[작업] 표지 D-day 계산 결함 수정 · 경과 시간 기준을 KST 달력 날짜 차이로 교정</t>
+          <t>[작업] 연구 허브 「후속 과제」 라벨 수와 칩 수 불일치 해소 · 상한 초과분 표기</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -12930,12 +12958,12 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>4600%</t>
+          <t>5300%</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -12962,42 +12990,28 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>(미분류)</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>[작업] 일정 허브 멘토링 D-day 주간 반복 반영 · 빌드 시점 고정값 제거</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>2</v>
-      </c>
+          <t>[승격 검토] inbox/meang/20260903-rails-diagnosis.md</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
+      <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>4600%</t>
-        </is>
-      </c>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
           <t>100%</t>
@@ -13008,11 +13022,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+      <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -13022,42 +13032,28 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>C2 운영</t>
+          <t>(미분류)</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>[작업] 연구 허브 「후속 과제」 라벨 수와 칩 수 불일치 해소 · 상한 초과분 표기</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>기획발표</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>2</v>
-      </c>
+          <t>[승격 검토] inbox/meang/20260903-rails-isaac-sweep-design.md</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
+      <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>4600%</t>
-        </is>
-      </c>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
           <t>100%</t>
@@ -13068,11 +13064,7 @@
           <t>vfxpedia</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>deliverables/plan/wbs.md</t>
-        </is>
-      </c>
+      <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
           <t>foothold-lab</t>
@@ -13087,7 +13079,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260903-rails-diagnosis.md</t>
+          <t>[승격 검토] inbox/lim/20260903_기본값_1500iter_학습지형결과분석.md</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -13100,7 +13092,7 @@
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
@@ -13129,7 +13121,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260903-rails-isaac-sweep-design.md</t>
+          <t>[승격 검토] inbox/meang/20260902-park-mentoring.md</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -13171,7 +13163,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/lim/20260903_기본값_1500iter_학습지형결과분석.md</t>
+          <t>[승격 검토] inbox/lee/20260902-브레인스토밍-입력본.txt</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -13184,7 +13176,7 @@
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
@@ -13213,7 +13205,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260902-park-mentoring.md</t>
+          <t>[승격 검토] inbox/jay/20260902-benchmark-setup-lim-지표표-정정안.md</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -13226,7 +13218,7 @@
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
@@ -13255,7 +13247,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/lee/20260902-브레인스토밍-입력본.txt</t>
+          <t>[승격 검토] inbox/jay/20260903-ending-title/foothold-ending-title.html</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -13268,7 +13260,7 @@
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
@@ -13297,20 +13289,20 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260902-benchmark-setup-lim-지표표-정정안.md</t>
+          <t>[승격 검토] inbox/jay/20260904-roughcut/foothold-roughcut.mp4</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
@@ -13339,14 +13331,14 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260903-ending-title/foothold-ending-title.html</t>
+          <t>[승격 검토] inbox/jay/20260904-roughcut/foothold-roughcut.mp4</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -13507,7 +13499,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260904-roughcut/foothold-roughcut.mp4</t>
+          <t>[승격 검토] inbox/jay/20260904-launch/.gitignore</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -13549,7 +13541,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260904-roughcut/foothold-roughcut.mp4</t>
+          <t>[승격 검토] inbox/jay/20260904-launch/.gitignore</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -13717,7 +13709,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260904-launch/.gitignore</t>
+          <t>[승격 검토] inbox/jay/20260904-launch/SOUND-CRITERIA.md</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -13730,7 +13722,7 @@
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
@@ -13759,7 +13751,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260904-launch/.gitignore</t>
+          <t>[승격 검토] inbox/jay/20260904-launch/CONVERSION.md</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -13801,7 +13793,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260904-launch/SOUND-CRITERIA.md</t>
+          <t>[승격 검토] inbox/jay/20260904-launch/CONVERSION.md</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -13843,7 +13835,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260904-launch/CONVERSION.md</t>
+          <t>[승격 검토] inbox/jay/20260904-launch/README-A.md</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -13856,7 +13848,7 @@
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
@@ -13885,20 +13877,20 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260904-launch/CONVERSION.md</t>
+          <t>[작업] 웹에 남은 ASCII 도식 3블록의 SVG 전환</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
@@ -13927,20 +13919,20 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260904-launch/README-A.md</t>
+          <t>[작업] 원장 전수 절의 자동 동기화</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
@@ -13969,7 +13961,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>[작업] 웹에 남은 ASCII 도식 3블록의 SVG 전환</t>
+          <t>[작업] 강화학습 멘토 첫 미팅 준비 (월 17:00)</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -13982,7 +13974,7 @@
       <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
@@ -14011,7 +14003,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>[작업] 원장 전수 절의 자동 동기화</t>
+          <t>[승격 검토] inbox/lim/20260904_NVIDIA공식체크포인트_속도단차교차평가분석.md</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -14024,7 +14016,7 @@
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H249" t="inlineStr"/>
@@ -14053,7 +14045,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>[작업] 강화학습 멘토 첫 미팅 준비 (월 17:00)</t>
+          <t>[승격 검토] inbox/meang/20260902-flat-straight-baseline-10m.md</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -14066,7 +14058,7 @@
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H250" t="inlineStr"/>
@@ -14095,7 +14087,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/lim/20260904_NVIDIA공식체크포인트_속도단차교차평가분석.md</t>
+          <t>[승격 검토] inbox/meang/20260903-직진성-외부표준.md</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -14137,7 +14129,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260902-flat-straight-baseline-10m.md</t>
+          <t>[승격 검토] inbox/meang/20260904-발보상-시간아니고높이아님.md</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -14179,7 +14171,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260903-직진성-외부표준.md</t>
+          <t>[승격 검토] inbox/meang/20260904-east-midterm-review.md</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -14192,7 +14184,7 @@
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H253" t="inlineStr"/>
@@ -14221,7 +14213,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260904-발보상-시간아니고높이아님.md</t>
+          <t>[승격 검토] inbox/jay/20260905-mentor-change.md</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -14234,7 +14226,7 @@
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H254" t="inlineStr"/>
@@ -14263,14 +14255,14 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260904-east-midterm-review.md</t>
+          <t>[승격 검토] inbox/meang/20260904-레일-보상-외부문헌.md</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -14305,14 +14297,14 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260905-mentor-change.md</t>
+          <t>[승격 검토] inbox/meang/20260906-rails-진단.md</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -14347,7 +14339,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260904-레일-보상-외부문헌.md</t>
+          <t>[승격 검토] inbox/lim/20260906_Pretrained_vs_Model99_difficulty05-07_7종지형성능보고서.md</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -14360,7 +14352,7 @@
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H257" t="inlineStr"/>
@@ -14389,7 +14381,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260906-rails-진단.md</t>
+          <t>[승격 검토] inbox/jay/20260907-go2-관절한계-실측.md</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -14431,20 +14423,20 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/lim/20260906_Pretrained_vs_Model99_difficulty05-07_7종지형성능보고서.md</t>
+          <t>[승격 검토] inbox/lee/20260908-pit진단.md</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H259" t="inlineStr"/>
@@ -14473,14 +14465,14 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260907-go2-관절한계-실측.md</t>
+          <t>[승격 검토] inbox/jay/20260908-go2-제원-시뮬실기-대조.md</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -14515,7 +14507,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/lee/20260908-pit진단.md</t>
+          <t>[승격 검토] inbox/jay/20260908-평가-성공기준-해부.md</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -14557,7 +14549,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260908-go2-제원-시뮬실기-대조.md</t>
+          <t>[승격 검토] inbox/jay/20260904-launch/ARCHIVE.md</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -14599,7 +14591,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260908-평가-성공기준-해부.md</t>
+          <t>[승격 검토] inbox/jay/20260903-render-blackframe/20260903-render-blackframe.md</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -14641,7 +14633,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260904-launch/ARCHIVE.md</t>
+          <t>[승격 검토] inbox/oh/20260908-평가하네스-수정본.md</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -14654,7 +14646,7 @@
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H264" t="inlineStr"/>
@@ -14683,14 +14675,14 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260903-render-blackframe/20260903-render-blackframe.md</t>
+          <t>[승격 검토] inbox/jay/20260904-launch/ARCHIVE.md</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -14725,14 +14717,14 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260908-평가하네스-수정본.md</t>
+          <t>[승격 검토] inbox/jay/20260909-parkour-ablation-대조분석.md</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -14767,7 +14759,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260904-launch/ARCHIVE.md</t>
+          <t>[승격 검토] inbox/jay/20260904-launch/README-B.md</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -14780,7 +14772,7 @@
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H267" t="inlineStr"/>
@@ -14809,7 +14801,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260909-parkour-ablation-대조분석.md</t>
+          <t>[승격 검토] inbox/jay/20260904-launch/design/STATUS.md</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -14851,31 +14843,27 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260904-launch/README-B.md</t>
+          <t>[작업] RL gap 40cm까지 추가 학습 및 검증</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
+      <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>vfxpedia</t>
+          <t>IQ152</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
@@ -14893,20 +14881,20 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260904-launch/design/STATUS.md</t>
+          <t>[승격 검토] inbox/jay/20260904-launch/keyvis/20260914-session1/astra/charsheet-review.md</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H270" t="inlineStr"/>
@@ -14935,27 +14923,31 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>[작업] RL gap 40cm까지 추가 학습 및 검증</t>
+          <t>[승격 검토] inbox/jay/20260918-v2-command-restore.md</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>IQ152</t>
+          <t>vfxpedia</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -14973,14 +14965,14 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260904-launch/keyvis/20260914-session1/astra/charsheet-review.md</t>
+          <t>[승격 검토] inbox/jay/20260916-3dgs-test/DESIGN-real-to-sim.md</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -15015,7 +15007,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260918-v2-command-restore.md</t>
+          <t>[승격 검토] inbox/jay/20260916-3dgs-test/20260916_prompt_01.md</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -15057,7 +15049,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260916-3dgs-test/DESIGN-real-to-sim.md</t>
+          <t>[승격 검토] inbox/jay/20260918-why-gap-fell-rails-rose.md</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -15099,14 +15091,14 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260916-3dgs-test/20260916_prompt_01.md</t>
+          <t>[승격 검토] inbox/jay/20260919-E-design.md</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -15141,14 +15133,14 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260918-why-gap-fell-rails-rose.md</t>
+          <t>[승격 검토] inbox/jay/20260920-E-run-status.md</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -15183,14 +15175,14 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260919-E-design.md</t>
+          <t>[승격 검토] inbox/jay/20260920-FG-design.md</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -15225,14 +15217,14 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260920-E-run-status.md</t>
+          <t>[작업] F·G 학습 설정과 고리 도랑 지형 구현 및 기하 노출 측정</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -15247,11 +15239,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>vfxpedia</t>
-        </is>
-      </c>
+      <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr">
         <is>
@@ -15267,14 +15255,14 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260920-FG-design.md</t>
+          <t>[승격 검토] inbox/jay/20260921-v2-design.md</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -15309,14 +15297,14 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>[작업] F·G 학습 설정과 고리 도랑 지형 구현 및 기하 노출 측정</t>
+          <t>[승격 검토] inbox/jay/20260921-two-axes-guide.md</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -15331,7 +15319,11 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="J280" t="inlineStr"/>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>vfxpedia</t>
+        </is>
+      </c>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr">
         <is>
@@ -15347,14 +15339,14 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260921-v2-design.md</t>
+          <t>[승격 검토] inbox/meang/20260909-영상재현-외부문헌/20260909-영상재현-외부문헌.md</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -15389,14 +15381,14 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260921-two-axes-guide.md</t>
+          <t>[승격 검토] inbox/meang/20260904-rails-난이도격자/20260904-rails-난이도격자.md</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
@@ -15431,7 +15423,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260909-영상재현-외부문헌/20260909-영상재현-외부문헌.md</t>
+          <t>[승격 검토] inbox/lim/20260910-최종 후보 선택.md</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -15473,7 +15465,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260904-rails-난이도격자/20260904-rails-난이도격자.md</t>
+          <t>[승격 검토] inbox/meang/20260818-rough-terrain-rl-study.md</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -15515,7 +15507,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/lim/20260910-최종 후보 선택.md</t>
+          <t>[승격 검토] inbox/meang/20260910-레일즈-학습레시피.md</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -15557,7 +15549,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260818-rough-terrain-rl-study.md</t>
+          <t>[승격 검토] inbox/oh/20260826-cv-단계별-계획과-환경.md</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -15599,7 +15591,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260910-레일즈-학습레시피.md</t>
+          <t>[승격 검토] inbox/oh/20260916-RL작업-상태정리-인계.md</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -15641,7 +15633,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260826-cv-단계별-계획과-환경.md</t>
+          <t>[승격 검토] inbox/meang/20260916-3DGS-실측정리.md</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -15683,7 +15675,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/oh/20260916-RL작업-상태정리-인계.md</t>
+          <t>[승격 검토] inbox/jay/20260929-locomotion-direction/DIRECTION.md</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -15696,7 +15688,7 @@
       <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H289" t="inlineStr"/>
@@ -15725,7 +15717,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20260916-3DGS-실측정리.md</t>
+          <t>[승격 검토] inbox/jay/20260916-3dgs-test/RESEARCH-3dgs-terrain.md</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -15767,7 +15759,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260929-locomotion-direction/DIRECTION.md</t>
+          <t>[승격 검토] inbox/jay/20260929-mvp-submission/CONTENT-MAP.md</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -15780,7 +15772,7 @@
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H291" t="inlineStr"/>
@@ -15809,7 +15801,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260916-3dgs-test/RESEARCH-3dgs-terrain.md</t>
+          <t>[승격 검토] inbox/jay/20260921-perception-research/BRIEF-codex-astra.md</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -15851,14 +15843,14 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260929-mvp-submission/CONTENT-MAP.md</t>
+          <t>[승격 검토] inbox/jay/20260930-mvp-brand/HANDOFF.md</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F293" t="inlineStr"/>
@@ -15893,20 +15885,20 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260921-perception-research/BRIEF-codex-astra.md</t>
+          <t>[승격 검토] inbox/meang/20261001-ops-mentoring.md</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H294" t="inlineStr"/>
@@ -15935,14 +15927,14 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260930-mvp-brand/HANDOFF.md</t>
+          <t>[승격 검토] inbox/jay/20261007-wip-request/TEMPLATE.md</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -15977,20 +15969,20 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20261001-ops-mentoring.md</t>
+          <t>[승격 검토] inbox/meang/20261007-underground-recon-evidence.md</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H296" t="inlineStr"/>
@@ -16019,7 +16011,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20261007-wip-request/TEMPLATE.md</t>
+          <t>[승격 검토] inbox/jay/20260929-mvp-presentation/SECTION-MAP.md</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
@@ -16030,15 +16022,11 @@
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -16061,26 +16049,22 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/meang/20261007-underground-recon-evidence.md</t>
+          <t>판단층 시연 범위와 기능 구체화 논의</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -16103,14 +16087,14 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>[승격 검토] inbox/jay/20260929-mvp-presentation/SECTION-MAP.md</t>
+          <t>[승격 검토] inbox/jay/AGENTS.md</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -16169,7 +16153,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>562%</t>
+          <t>650%</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -16229,7 +16213,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>562%</t>
+          <t>650%</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -16289,7 +16273,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>562%</t>
+          <t>650%</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -16349,7 +16333,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>562%</t>
+          <t>650%</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -16409,7 +16393,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>562%</t>
+          <t>650%</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -16469,7 +16453,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>1025%</t>
+          <t>1200%</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -16529,7 +16513,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>1025%</t>
+          <t>1200%</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -16589,7 +16573,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>1333%</t>
+          <t>1567%</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
